--- a/data_kr/weekly_data/sector_daily_20261026.xlsx
+++ b/data_kr/weekly_data/sector_daily_20261026.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1075,14 +1075,421 @@
       </c>
       <c r="E28" s="7" t="inlineStr"/>
     </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>🌐 글로벌 코멘트 (미국장 마감)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>① 섹터 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1D 기준 일본 TOPIX 제약(+1.7%)이 TOPIX(+0.5%)를, 유럽 헬스케어 EXV4(+0.7%)가 MSCI 유럽(+0.3%)을 상회했다. 미국 XLV(+0.0%)는 S&amp;P500(+0.7%)에 뒤처졌다.</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>20일 누적 상위는 GL 진단(PCR) +20.6%·안과 +13.4%, 하위는 DNA 합성 -16.7%·국내 관련 -15.2%다. 10.26 단일일은 당뇨/디지털헬스(+3.1%)가 가장 강하고 PD-1xVEGF(-4.6%)가 가장 약했다.</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>10.22~10.26 중 중국 바이오(2820.HK)는 10.22 -4.9%·10.23 +2.2%로 변동이 가장 컸고, 미국 XBI는 3일 중 2일 하락했다.</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="31" customHeight="1">
+      <c r="A38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>글로벌 CDMO(Lonza 20D +12.8%)는 강하고 시밀러 내 Biocon(-17.1%)·Alvotech(-20.9%)는 약해, 국내 바이오 위탁생산 대비 시밀러 가격 압력을 주의해야 한다.</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="31" customHeight="1">
+      <c r="A39" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>미 10년물이 4.95%에서 4.99%로 올라온 가운데 원달러는 1,326에서 1,325로 보합이다. XBI 반등(10.26 +0.6%)이 금리 고점 구간에서 이어지는지 확인이 필요하다.</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>② 종목 코멘트</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>등락</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Merck &amp; Co (미국)</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>-3.2%</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 빅파마 중 단독 약세로 섹터 동반은 아님. 20D -6.8%로 하락 추세가 이어진다.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Summit (미국)</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>-6.3%</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>담도암 확장·생존 혜택 보고 등 긍정 임상 뉴스에도 1D -6.3%, 5D -6.9%로 약세. 원인은 확인되지 않았다.</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>오릭 파마 (미국)</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>-32.0%</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>10.26 단일일 -32.0%(5D -29.6%)로 개별 급락 성격이 강하다. 관련 뉴스·공시는 확인되지 않아 원인 미확인.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="17.5" customHeight="1">
+      <c r="A46" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>메타비아 (미국)</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>-12.0%</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 1D -12.0%의 단독 급락이다. 10월 공시·뉴스는 검색되지 않아 원인 미확인.</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr"/>
+    </row>
+    <row r="47" ht="31" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>탠덤 (미국)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>+8.4%</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 최근 5일 누적 +15.4%로 강세가 이어졌다. 10월 공시·뉴스는 확인되지 않았다.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="17.5" customHeight="1">
+      <c r="A48" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>ADMA (미국)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>+3.6%</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 5D 보합(-0.0%)에서 1D만 +3.6%로 단기 반등 성격이다.</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr"/>
+    </row>
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>패썸 파마 (미국)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>+3.5%</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 5D -15.3% 급락 뒤 1D +3.5% 반등이다. 20D -23.5%로 추세는 여전히 약하다.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>UCB (벨기에)</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 5D +31.7%·20D +26.6% 급등 뒤 1D -0.9%로 진정됐다. 급등 원인은 확인되지 않았다.</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Alnylam (미국)</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>+1.6%</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 10.23 헌팅턴병 브레조시란(ALN-HTT02) 1b상 초기 데이터 긍정 발표에도 주가 반응은 제한적이다(20D -9.5%).</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="31" customHeight="1">
+      <c r="A52" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>일루미나 (미국)</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 10.23 NovaSeq X 수요 강세 보도 후 1D +0.6%로 제한적이다. 20D +9.5%로 이미 선반영된 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Tempus AI (미국)</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>10.26 xR RNA 시퀀싱 IVDR 인증 보도에도 1D -0.7%로 반응이 미미하다. 20D -13.0%로 약세가 이어진다. IVDR 인증은 교차확인되지 않았다.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="31" customHeight="1">
+      <c r="A54" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Telix Pharma (호주)</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 5D -16.3%·20D -24.8%로 약세가 지속된다. [추정] 밸류에이션 조정 흐름으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="14">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2202,10 +2609,10 @@
         <v>-0.006149937285433264</v>
       </c>
       <c r="U19" s="22" t="n">
-        <v>-0.0003378027232096508</v>
+        <v>-0.004585112879195423</v>
       </c>
       <c r="V19" s="22" t="n">
-        <v>-0.1498155686764877</v>
+        <v>-0.1531084759073714</v>
       </c>
     </row>
     <row r="20">
@@ -2272,10 +2679,10 @@
         <v>-0.005112353352273535</v>
       </c>
       <c r="U20" s="22" t="n">
-        <v>0.002525396373302957</v>
+        <v>0.01854630780299037</v>
       </c>
       <c r="V20" s="22" t="n">
-        <v>-0.138591160339667</v>
+        <v>-0.1259413261090872</v>
       </c>
     </row>
     <row r="21">
@@ -2342,10 +2749,10 @@
         <v>-0.003174567658130079</v>
       </c>
       <c r="U21" s="22" t="n">
-        <v>-0.001607212857702867</v>
+        <v>0.009547128132854299</v>
       </c>
       <c r="V21" s="22" t="n">
-        <v>-0.2326590588215318</v>
+        <v>-0.2245380639089124</v>
       </c>
     </row>
     <row r="22">
@@ -2412,10 +2819,10 @@
         <v>0.008234040195020801</v>
       </c>
       <c r="U22" s="22" t="n">
-        <v>-0.0032878905136509</v>
+        <v>0.01111154755888828</v>
       </c>
       <c r="V22" s="22" t="n">
-        <v>-0.07514107741983686</v>
+        <v>-0.06180501439481684</v>
       </c>
     </row>
     <row r="23">
@@ -2482,10 +2889,10 @@
         <v>-0.002119072935428395</v>
       </c>
       <c r="U23" s="22" t="n">
-        <v>-0.01582935637744281</v>
+        <v>-0.007212246036918341</v>
       </c>
       <c r="V23" s="22" t="n">
-        <v>-0.130170851020381</v>
+        <v>-0.1234553752490298</v>
       </c>
     </row>
     <row r="24">
@@ -2552,10 +2959,10 @@
         <v>-0.002733574016911814</v>
       </c>
       <c r="U24" s="22" t="n">
-        <v>-0.01439813989494914</v>
+        <v>-0.008344874562968951</v>
       </c>
       <c r="V24" s="22" t="n">
-        <v>-0.06544095598724184</v>
+        <v>-0.06005226380915093</v>
       </c>
     </row>
     <row r="25">
@@ -2622,10 +3029,10 @@
         <v>-0.002066590869575147</v>
       </c>
       <c r="U25" s="22" t="n">
-        <v>-0.002186623708569294</v>
+        <v>0.003360646900885578</v>
       </c>
       <c r="V25" s="22" t="n">
-        <v>-0.06163214542487823</v>
+        <v>-0.05786355978346081</v>
       </c>
     </row>
     <row r="26">
@@ -2692,10 +3099,10 @@
         <v>-0.00446818059276574</v>
       </c>
       <c r="U26" s="22" t="n">
-        <v>6.934908376508749e-05</v>
+        <v>0.0004967383909154632</v>
       </c>
       <c r="V26" s="22" t="n">
-        <v>-0.06154662173300918</v>
+        <v>-0.06056919089125846</v>
       </c>
     </row>
     <row r="27">
@@ -2762,10 +3169,10 @@
         <v>-0.00330548146494255</v>
       </c>
       <c r="U27" s="22" t="n">
-        <v>-0.006864144343610723</v>
+        <v>0.02166023893918193</v>
       </c>
       <c r="V27" s="22" t="n">
-        <v>-0.1728583040936602</v>
+        <v>-0.1496861739542931</v>
       </c>
     </row>
     <row r="28">
@@ -2832,10 +3239,10 @@
         <v>-0.005358795849538522</v>
       </c>
       <c r="U28" s="22" t="n">
-        <v>-0.001719262005324088</v>
+        <v>0.003776683295047586</v>
       </c>
       <c r="V28" s="22" t="n">
-        <v>-0.1608054443530018</v>
+        <v>-0.1564714280609373</v>
       </c>
     </row>
     <row r="29">
@@ -2902,10 +3309,10 @@
         <v>0.0009665285215805416</v>
       </c>
       <c r="U29" s="22" t="n">
-        <v>-0.006545042259327967</v>
+        <v>-0.01702388769499141</v>
       </c>
       <c r="V29" s="22" t="n">
-        <v>-0.152481569433195</v>
+        <v>-0.1600209850130248</v>
       </c>
     </row>
     <row r="30">
@@ -2972,10 +3379,10 @@
         <v>0.01377172828856669</v>
       </c>
       <c r="U30" s="22" t="n">
-        <v>0</v>
+        <v>0.04536236978118032</v>
       </c>
       <c r="V30" s="22" t="n">
-        <v>-0.0909978045356874</v>
+        <v>-0.05201974197416489</v>
       </c>
     </row>
   </sheetData>
@@ -3498,7 +3905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3960,14 +4367,409 @@
       </c>
       <c r="E27" s="10" t="inlineStr"/>
     </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>🌐 글로벌 코멘트 (미국장 마감)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>① 섹터 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+    </row>
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>미국 LIT 10.26 +1.0%로 NASDAQ(+0.8%)·S&amp;P500(+0.7%)을 소폭 상회. 중국 지수는 10.26 전부 0.0%라 데이터 확인 필요.</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>10.26 1D 장비·부품 +2.7%·리튬 +1.4%가 상위, ESS -2.1%·EV -0.4%가 하위. 20일 누적은 장비·부품 -5.1%로 상대적으로 견조, 리튬 -26.0%로 최약.</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>국가 1D 평균은 AU +8.4%·BE +2.6%가 상위, US -0.8%·JP -0.5%가 하위이며 CN은 +0.6%로 중립. AU·BE는 1종목 표본이라 해석 제한.</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>셀 내 차별화가 커서(CATL 5D -19.1% vs EVE 5D +4.8%) 한국 셀 밸류체인도 고객사 믹스와 수주 확인이 우선.</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="17.5" customHeight="1">
+      <c r="A38" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>점검: 미 10년물 4.99%(10.22 4.95%에서 상승) 유지 여부, 원달러 1,325 수준 지속 여부, 중국 지수 0.0% 데이터 정정 여부.</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>② 종목 코멘트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>등락</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Tesla (US)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>+5.2%</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>10.26 +5.2%의 직접 원인은 미확인. [추정] 10.23 3Q 실적 상회와 SpaceX 합병 검토 보도로 재평가 기대가 되살아났을 가능성.</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 10.23 테슬라 3Q 실적·SpaceX 합병 보도</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>CATL (CN)</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 다만 1D 0.0%는 5D -19.1%와 어긋나 데이터 확인 필요.</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>EVE Energy (CN)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>+6.5%</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 셀 그룹 +0.5%를 크게 앞서 개별 수급 영향 [추정].</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>BYD (CN)</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 20D -13.0%로 GL EV 누적(-10.1%)보다 낙폭이 큼.</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46" ht="31" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Panasonic (JP)</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 5D -10.0%·20D -16.5%로 셀 그룹 20일 누적(-12.8%)보다 약세가 큼.</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="31" customHeight="1">
+      <c r="A47" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Pilbara (AU)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>+8.4%</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 리튬 그룹 +1.4%를 크게 상회하고 5D -2.1%라 단기 반등 성격 [추정].</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr"/>
+    </row>
+    <row r="48" ht="31" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Albemarle (US)</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 20D -20.0%로 리튬 그룹 누적(-26.0%)보다 낙폭이 작음.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>SQM (CL)</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 5D -5.3%·20D -18.8%로 리튬 내에서 최근 약세가 상대적으로 큼.</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr"/>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Umicore (BE)</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>+2.6%</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 5D -9.2% 이후 1D 반등, 소재 그룹 +0.6%를 웃도는 개별 강세 [추정].</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="A51" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Kedali (CN)</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 장비·부품 그룹 +2.7%와 같은 방향이며 5D +9.8%로 강세 지속.</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr"/>
+    </row>
+    <row r="52" ht="31" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Enovix (US)</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>-3.9%</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. ESS 그룹 -2.1%보다 낙폭이 커 5D +14.0% 이후 차익 실현 성격 [추정].</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>QuantumScape (US)</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>-3.2%</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. ESS 그룹과 같은 방향이며 20D -22.8%로 누적 약세가 이어짐.</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="14">
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4144,22 +4946,22 @@
         </is>
       </c>
       <c r="L5" s="21" t="n">
-        <v>4.98799991607666</v>
+        <v>4.986000061035156</v>
       </c>
       <c r="M5" s="21" t="n">
-        <v>0</v>
+        <v>-0.001999855041503906</v>
       </c>
       <c r="N5" s="21" t="n">
-        <v>-0.1480002403259277</v>
+        <v>-0.1500000953674316</v>
       </c>
       <c r="O5" s="21" t="n">
-        <v>-0.1960000991821289</v>
+        <v>-0.1979999542236328</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>0.3090000152587891</v>
+        <v>0.3070001602172852</v>
       </c>
       <c r="Q5" s="21" t="n">
-        <v>0.8249998092651367</v>
+        <v>0.8229999542236328</v>
       </c>
     </row>
     <row r="6">
@@ -4202,22 +5004,22 @@
         </is>
       </c>
       <c r="L6" s="21" t="n">
-        <v>1323.0400390625</v>
+        <v>1325.170043945312</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>-2.949951171875</v>
+        <v>-0.8199462890625</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>-10.3900146484375</v>
+        <v>-8.260009765625</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>-44.3199462890625</v>
+        <v>-42.18994140625</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>-151</v>
+        <v>-148.8699951171875</v>
       </c>
       <c r="Q6" s="21" t="n">
-        <v>-114.8699951171875</v>
+        <v>-112.739990234375</v>
       </c>
     </row>
     <row r="7">
@@ -4260,22 +5062,22 @@
         </is>
       </c>
       <c r="L7" s="21" t="n">
-        <v>6.667600154876709</v>
+        <v>6.659299850463867</v>
       </c>
       <c r="M7" s="21" t="n">
-        <v>-0.0102996826171875</v>
+        <v>-0.0185999870300293</v>
       </c>
       <c r="N7" s="21" t="n">
-        <v>-0.0232996940612793</v>
+        <v>-0.03159999847412109</v>
       </c>
       <c r="O7" s="21" t="n">
-        <v>-0.04349994659423828</v>
+        <v>-0.05180025100708008</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>-0.1048998832702637</v>
+        <v>-0.1132001876831055</v>
       </c>
       <c r="Q7" s="21" t="n">
-        <v>-0.3284997940063477</v>
+        <v>-0.3368000984191895</v>
       </c>
     </row>
     <row r="8">
@@ -4350,22 +5152,22 @@
         </is>
       </c>
       <c r="C10" s="21" t="n">
-        <v>25955.33984375</v>
+        <v>26169.380859375</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>0</v>
+        <v>0.008246511774205878</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.01799223446523568</v>
+        <v>-0.009894095864391605</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.0411316394145832</v>
+        <v>-0.03322432018910204</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0.03921871309907554</v>
+        <v>0.04778864245262215</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>0.1167434278223707</v>
+        <v>0.1259526656486749</v>
       </c>
     </row>
     <row r="11">
@@ -4380,22 +5182,22 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>7623.68017578125</v>
+        <v>7676.77001953125</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>0</v>
+        <v>0.006963807836358971</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-0.008718262747200667</v>
+        <v>-0.001815167217280034</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.01546217726463983</v>
+        <v>-0.008606045059483591</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>0.02856189518459984</v>
+        <v>0.0357246025704665</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0.1136776241006865</v>
+        <v>0.1214330610665766</v>
       </c>
     </row>
     <row r="12">
@@ -4410,22 +5212,22 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>60.68000030517578</v>
+        <v>61.27000045776367</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>0</v>
+        <v>0.009723140237650307</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.06082650159495795</v>
+        <v>-0.051694785962481</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.1208344935312082</v>
+        <v>-0.1122862440197073</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>-0.1051466968017073</v>
+        <v>-0.09644591264258562</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>-0.06444650425286391</v>
+        <v>-0.05534998641389055</v>
       </c>
     </row>
     <row r="13">
@@ -4440,22 +5242,22 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>3690.055908203125</v>
+        <v>3690.47509765625</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>-0.0001135868531916273</v>
+        <v>0</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.01095279837883478</v>
+        <v>-0.01084044285743457</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.05100283924308613</v>
+        <v>-0.05089503339658108</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>-0.03254736379897405</v>
+        <v>-0.03243746141494996</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>-0.07024323820405409</v>
+        <v>-0.07013761806218843</v>
       </c>
     </row>
     <row r="14">
@@ -4470,22 +5272,22 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>2.651000022888184</v>
+        <v>2.70199990272522</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>-0.01887486368359892</v>
+        <v>0</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.04018829024707482</v>
+        <v>-0.02172345379254714</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.1995772965334645</v>
+        <v>-0.1841787822584041</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.2442987170116826</v>
+        <v>-0.2297605524351658</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>-0.1679221806573692</v>
+        <v>-0.151914685962856</v>
       </c>
     </row>
     <row r="15">
@@ -4500,22 +5302,22 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>23199.2890625</v>
+        <v>23093.369140625</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>0.004586594586091453</v>
+        <v>0</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.04082969998280794</v>
+        <v>-0.0452089394917834</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.05348004799681505</v>
+        <v>-0.05780153039652192</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>-0.07066158398281719</v>
+        <v>-0.07490462143774901</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>-0.09485754451248185</v>
+        <v>-0.09899011158868398</v>
       </c>
     </row>
     <row r="17">
@@ -4933,13 +5735,13 @@
         </is>
       </c>
       <c r="I28" s="22" t="n">
-        <v>0</v>
+        <v>0.008246511774205878</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>0</v>
+        <v>0.006963807836358971</v>
       </c>
       <c r="K28" s="22" t="n">
-        <v>0</v>
+        <v>0.009723140237650307</v>
       </c>
     </row>
     <row r="30">
@@ -5273,13 +6075,13 @@
         </is>
       </c>
       <c r="B41" s="22" t="n">
-        <v>-0.0001135868531916273</v>
+        <v>0</v>
       </c>
       <c r="C41" s="22" t="n">
-        <v>-0.01887486368359892</v>
+        <v>0</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>0.004586594586091453</v>
+        <v>0</v>
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
@@ -5287,13 +6089,13 @@
         </is>
       </c>
       <c r="I41" s="21" t="n">
-        <v>4.98799991607666</v>
+        <v>4.986000061035156</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>1323.0400390625</v>
+        <v>1325.170043945312</v>
       </c>
       <c r="K41" s="21" t="n">
-        <v>6.667600154876709</v>
+        <v>6.659299850463867</v>
       </c>
     </row>
     <row r="43">
@@ -8592,11 +9394,11 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>Mercedes-Benz (DE)</t>
+          <t>Tianneng (CN)</t>
         </is>
       </c>
       <c r="F5" s="22" t="n">
-        <v>0</v>
+        <v>-0.01167882114158159</v>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
@@ -8617,200 +9419,200 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>0.06383933903595995</v>
+        <v>0.06496722613262862</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Sigma Lithium (CA)</t>
+          <t>Li Auto (CN)</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0</v>
+        <v>-0.01375338778613189</v>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>CN (21종목)</t>
+          <t>BE (1종목)</t>
         </is>
       </c>
       <c r="J6" s="22" t="n">
-        <v>0.00714609732385871</v>
+        <v>0.02555171612093998</v>
       </c>
       <c r="K6" s="22" t="n">
-        <v>0.004030732843997242</v>
+        <v>0.02555171612093998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Kedali (CN)</t>
+          <t>Tesla (US)</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>0.0380487069110087</v>
+        <v>0.05211969757901702</v>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>Shanshan(음극) (CN)</t>
+          <t>Panasonic (JP)</t>
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>-0.006597520932073331</v>
+        <v>-0.01377031120903327</v>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>BE (1종목)</t>
+          <t>DE (3종목)</t>
         </is>
       </c>
       <c r="J7" s="22" t="n">
-        <v>0</v>
+        <v>0.008073563733961139</v>
       </c>
       <c r="K7" s="22" t="n">
-        <v>0</v>
+        <v>0.0055730323881229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Tianqi (CN)</t>
+          <t>Kedali (CN)</t>
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>0.02480752542880071</v>
+        <v>0.03856289055351581</v>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Xiamen Tungsten NE(양극) (CN)</t>
+          <t>Fluence (US)</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>-0.007766494760103715</v>
+        <v>-0.01610020574797755</v>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>CA (1종목)</t>
+          <t>CN (21종목)</t>
         </is>
       </c>
       <c r="J8" s="22" t="n">
-        <v>0</v>
+        <v>0.005955393385897461</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0</v>
+        <v>0.00490438374022184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Semcorp(분리막) (CN)</t>
+          <t>Umicore (BE)</t>
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>0.02365730293413004</v>
+        <v>0.02555171612093998</v>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>Tianneng (CN)</t>
+          <t>Capchem(전해액) (CN)</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-0.01021893369325144</v>
+        <v>-0.0214101114964611</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>CL (1종목)</t>
+          <t>CA (1종목)</t>
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0</v>
+        <v>0.003831444457300881</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>0</v>
+        <v>0.003831444457300881</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Putailai(음극) (CN)</t>
+          <t>Tianqi (CN)</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0.02071752543934546</v>
+        <v>0.02480752542880071</v>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>BYD (CN)</t>
+          <t>Sunwoda (CN)</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.01117312066218035</v>
+        <v>-0.02403840128721579</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>DE (3종목)</t>
+          <t>CL (1종목)</t>
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0</v>
+        <v>-0.002975116744157846</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0</v>
+        <v>-0.002975116744157846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Ganfeng (CN)</t>
+          <t>Semcorp(분리막) (CN)</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0.01687385226653482</v>
+        <v>0.02365730293413004</v>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>Li Auto (CN)</t>
+          <t>Lithium Americas (US)</t>
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.01330972192652025</v>
+        <v>-0.02415456711535047</v>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>US (11종목)</t>
+          <t>JP (2종목)</t>
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0</v>
+        <v>-0.004952788454758217</v>
       </c>
       <c r="K11" s="22" t="n">
-        <v>0</v>
+        <v>-0.004952788454758217</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>CATL (CN)</t>
+          <t>Putailai(음극) (CN)</t>
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>0.01681614407308074</v>
+        <v>0.0212227463120418</v>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Panasonic (JP)</t>
+          <t>QuantumScape (US)</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.01377031120903327</v>
+        <v>-0.0322580912339705</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>JP (2종목)</t>
+          <t>US (11종목)</t>
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>-0.004952788454758217</v>
+        <v>-0.00753740922445666</v>
       </c>
       <c r="K12" s="22" t="n">
-        <v>-0.004952788454758217</v>
+        <v>-0.002668944217860347</v>
       </c>
     </row>
     <row r="13">
@@ -8820,33 +9622,33 @@
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>0.01459290120608303</v>
+        <v>0.01689702808138605</v>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>Capchem(전해액) (CN)</t>
+          <t>Rivian (US)</t>
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.0217792598473473</v>
+        <v>-0.03381230947674962</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Wuxi Lead (CN)</t>
+          <t>Ganfeng (CN)</t>
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0.0138157921567188</v>
+        <v>0.01687385226653482</v>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Sunwoda (CN)</t>
+          <t>Enovix (US)</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.02403840128721579</v>
+        <v>-0.03942648623649692</v>
       </c>
     </row>
     <row r="15">
@@ -8856,7 +9658,7 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>0.03171385696882172</v>
+        <v>0.03686294656455498</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
@@ -8864,7 +9666,7 @@
         </is>
       </c>
       <c r="F15" s="28" t="n">
-        <v>-0.01086537643177254</v>
+        <v>-0.02304026927309687</v>
       </c>
     </row>
     <row r="17">
@@ -8974,17 +9776,17 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Li Auto (CN)</t>
+          <t>Tesla (US)</t>
         </is>
       </c>
       <c r="B19" s="31" t="n">
-        <v>-0.01330972192652025</v>
+        <v>0.05211969757901702</v>
       </c>
       <c r="C19" s="31" t="n">
-        <v>-0.006255558306448195</v>
+        <v>0.06401129629644986</v>
       </c>
       <c r="D19" s="31" t="n">
-        <v>-0.01330972192652025</v>
+        <v>0.03357086678702403</v>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
@@ -9006,13 +9808,13 @@
         </is>
       </c>
       <c r="L19" s="31" t="n">
-        <v>0.01459290120608303</v>
+        <v>0.01689702808138605</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>-0.03470956279905113</v>
+        <v>-0.03251740115847213</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>-0.04724123647918155</v>
+        <v>-0.0450775341015095</v>
       </c>
       <c r="P19" s="29" t="inlineStr">
         <is>
@@ -9020,29 +9822,29 @@
         </is>
       </c>
       <c r="Q19" s="31" t="n">
-        <v>0</v>
+        <v>-0.002975116744157846</v>
       </c>
       <c r="R19" s="31" t="n">
-        <v>-0.04972562157582072</v>
+        <v>-0.0525527987906147</v>
       </c>
       <c r="S19" s="31" t="n">
-        <v>-0.185923957798004</v>
+        <v>-0.188345929062177</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Tesla (US)</t>
+          <t>Li Auto (CN)</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>0</v>
+        <v>-0.01375338778613189</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>0.01130251505108792</v>
+        <v>-0.006702396074850236</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>-0.0176299624792452</v>
+        <v>-0.01375338778613189</v>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
@@ -9050,13 +9852,13 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>0</v>
+        <v>0.0055730323881229</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>0.009138780828150006</v>
+        <v>0.01476274393781596</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>-0.03625383678628091</v>
+        <v>-0.03088284820476173</v>
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
@@ -9078,13 +9880,13 @@
         </is>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>0</v>
+        <v>-0.002668944217860347</v>
       </c>
       <c r="R20" s="22" t="n">
-        <v>-0.01024937898308165</v>
+        <v>-0.01289096818016855</v>
       </c>
       <c r="S20" s="22" t="n">
-        <v>-0.198030858548547</v>
+        <v>-0.2001712694515262</v>
       </c>
     </row>
     <row r="21">
@@ -9094,13 +9896,13 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0</v>
+        <v>-0.009118532443044058</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>-0.02949856635888637</v>
+        <v>-0.03834811516756365</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>-0.1155914149059423</v>
+        <v>-0.1236559232820291</v>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
@@ -9108,13 +9910,13 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>0</v>
+        <v>0.01546384947134039</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>-0.0001226470376480826</v>
+        <v>0.01533930583836418</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>-0.06280192007301189</v>
+        <v>-0.04830923004019161</v>
       </c>
       <c r="K21" s="20" t="inlineStr">
         <is>
@@ -9122,13 +9924,13 @@
         </is>
       </c>
       <c r="L21" s="22" t="n">
-        <v>0.06383933903595995</v>
+        <v>0.06496722613262862</v>
       </c>
       <c r="M21" s="22" t="n">
-        <v>0.04706924708684679</v>
+        <v>0.04817935445905408</v>
       </c>
       <c r="N21" s="22" t="n">
-        <v>-0.06706230347800024</v>
+        <v>-0.06607319887235885</v>
       </c>
       <c r="P21" s="20" t="inlineStr">
         <is>
@@ -9148,17 +9950,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Xpeng (CN)</t>
+          <t>BYD (CN)</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>0</v>
+        <v>-0.01117312066218035</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0</v>
+        <v>-0.03999995862023309</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>-0.1211831640804013</v>
+        <v>-0.1296864858051525</v>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
@@ -9166,13 +9968,13 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0</v>
+        <v>0.00318380934242013</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>-0.005469269781988029</v>
+        <v>-0.002302873551795925</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>-0.08136137526274856</v>
+        <v>-0.07843660502700212</v>
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
@@ -9180,13 +9982,13 @@
         </is>
       </c>
       <c r="L22" s="22" t="n">
-        <v>-0.01021893369325144</v>
+        <v>-0.01167882114158159</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>-0.05042012092563841</v>
+        <v>-0.05182071323219795</v>
       </c>
       <c r="N22" s="22" t="n">
-        <v>-0.1417721357010934</v>
+        <v>-0.1430379874430067</v>
       </c>
       <c r="P22" s="20" t="inlineStr">
         <is>
@@ -9194,29 +9996,29 @@
         </is>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0</v>
+        <v>0.003831444457300881</v>
       </c>
       <c r="R22" s="22" t="n">
-        <v>-0.07556084098534033</v>
+        <v>-0.07201890369342179</v>
       </c>
       <c r="S22" s="22" t="n">
-        <v>-0.2599243875076236</v>
+        <v>-0.2570888289041561</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>BYD (CN)</t>
+          <t>Xpeng (CN)</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>-0.01117312066218035</v>
+        <v>-0.009772003497841242</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>-0.03999995862023309</v>
+        <v>-0.009772003497841242</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>-0.1296864858051525</v>
+        <v>-0.1297709652749695</v>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
@@ -9224,13 +10026,13 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>0</v>
+        <v>0.005136978385860358</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>-0.08253778647800225</v>
+        <v>-0.0778248029172961</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>-0.090233661529876</v>
+        <v>-0.08556021151297166</v>
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
@@ -9248,17 +10050,17 @@
       </c>
       <c r="P23" s="20" t="inlineStr">
         <is>
-          <t>Lithium Americas (US)</t>
+          <t>Pilbara (AU)</t>
         </is>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>0</v>
+        <v>0.08396948023655493</v>
       </c>
       <c r="R23" s="22" t="n">
-        <v>-0.03271035898594565</v>
+        <v>-0.02068971697413624</v>
       </c>
       <c r="S23" s="22" t="n">
-        <v>-0.3100000222524008</v>
+        <v>-0.3123487081177079</v>
       </c>
     </row>
     <row r="24">
@@ -9268,55 +10070,55 @@
         </is>
       </c>
       <c r="B24" s="31" t="n">
+        <v>-0.03381230947674962</v>
+      </c>
+      <c r="C24" s="31" t="n">
+        <v>-0.07374390892704064</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>-0.2450462321015209</v>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>Ford (US)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="n">
+        <v>-0.001724177336719812</v>
+      </c>
+      <c r="H24" s="22" t="n">
+        <v>-0.04926111382893494</v>
+      </c>
+      <c r="I24" s="22" t="n">
+        <v>-0.1160305659161468</v>
+      </c>
+      <c r="K24" s="29" t="inlineStr">
+        <is>
+          <t>CATL (CN)</t>
+        </is>
+      </c>
+      <c r="L24" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="31" t="n">
-        <v>-0.04132902938213345</v>
-      </c>
-      <c r="D24" s="31" t="n">
-        <v>-0.2186261786365493</v>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>Ford (US)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="22" t="n">
-        <v>-0.04761904016205887</v>
-      </c>
-      <c r="I24" s="22" t="n">
-        <v>-0.114503813459562</v>
-      </c>
-      <c r="K24" s="29" t="inlineStr">
-        <is>
-          <t>CATL (CN)</t>
-        </is>
-      </c>
-      <c r="L24" s="31" t="n">
-        <v>0.01681614407308074</v>
-      </c>
       <c r="M24" s="31" t="n">
-        <v>-0.1769510030854048</v>
+        <v>-0.190562618707359</v>
       </c>
       <c r="N24" s="31" t="n">
-        <v>-0.2844181700335922</v>
+        <v>-0.2962524895602194</v>
       </c>
       <c r="P24" s="20" t="inlineStr">
         <is>
-          <t>Pilbara (AU)</t>
+          <t>Ganfeng (CN)</t>
         </is>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>0.08396948023655493</v>
+        <v>0.01687385226653482</v>
       </c>
       <c r="R24" s="22" t="n">
-        <v>-0.02068971697413624</v>
+        <v>-0.04424038006868369</v>
       </c>
       <c r="S24" s="22" t="n">
-        <v>-0.3123487081177079</v>
+        <v>-0.3131373871108771</v>
       </c>
     </row>
     <row r="25">
@@ -9326,13 +10128,13 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>-0.004080473764783432</v>
+        <v>-0.004251609381155023</v>
       </c>
       <c r="C25" s="28" t="n">
-        <v>-0.01763009960276886</v>
+        <v>-0.01742584766517983</v>
       </c>
       <c r="D25" s="28" t="n">
-        <v>-0.1026711546389685</v>
+        <v>-0.10139035457713</v>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
@@ -9340,13 +10142,13 @@
         </is>
       </c>
       <c r="G25" s="31" t="n">
-        <v>0</v>
+        <v>0.004926103745908295</v>
       </c>
       <c r="H25" s="31" t="n">
-        <v>-0.05361305853581866</v>
+        <v>-0.0489510582783933</v>
       </c>
       <c r="I25" s="31" t="n">
-        <v>-0.1594202884242891</v>
+        <v>-0.1552795055583616</v>
       </c>
       <c r="K25" s="26" t="inlineStr">
         <is>
@@ -9354,27 +10156,27 @@
         </is>
       </c>
       <c r="L25" s="28" t="n">
-        <v>0.007870123020937203</v>
+        <v>0.005396120096030669</v>
       </c>
       <c r="M25" s="28" t="n">
-        <v>-0.05021214115922223</v>
+        <v>-0.05216379764517681</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>-0.1262606126614515</v>
+        <v>-0.1279185067089894</v>
       </c>
       <c r="P25" s="29" t="inlineStr">
         <is>
-          <t>Ganfeng (CN)</t>
+          <t>Lithium Americas (US)</t>
         </is>
       </c>
       <c r="Q25" s="31" t="n">
-        <v>0.01687385226653482</v>
+        <v>-0.02415456711535047</v>
       </c>
       <c r="R25" s="31" t="n">
-        <v>-0.04424038006868369</v>
+        <v>-0.05607482153980292</v>
       </c>
       <c r="S25" s="31" t="n">
-        <v>-0.3131373871108771</v>
+        <v>-0.3266666730244955</v>
       </c>
     </row>
     <row r="26">
@@ -9384,13 +10186,13 @@
         </is>
       </c>
       <c r="G26" s="28" t="n">
-        <v>0.0005521048999309766</v>
+        <v>0.005203475756635585</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>-0.02505534731791327</v>
+        <v>-0.02048602983689531</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>-0.07345166748503894</v>
+        <v>-0.06915510615984852</v>
       </c>
       <c r="P26" s="26" t="inlineStr">
         <is>
@@ -9398,13 +10200,13 @@
         </is>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>0.01795012256169864</v>
+        <v>0.01424052490168895</v>
       </c>
       <c r="R26" s="28" t="n">
-        <v>-0.03295226566105715</v>
+        <v>-0.03656530732874567</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>-0.2575651106648142</v>
+        <v>-0.2601927498556398</v>
       </c>
     </row>
     <row r="27">
@@ -9507,13 +10309,13 @@
         </is>
       </c>
       <c r="L29" s="22" t="n">
-        <v>0.0138157921567188</v>
+        <v>0.01447370195983222</v>
       </c>
       <c r="M29" s="22" t="n">
-        <v>0.01582068358016753</v>
+        <v>0.01647989444579334</v>
       </c>
       <c r="N29" s="22" t="n">
-        <v>-0.04582042034658007</v>
+        <v>-0.04520121111326447</v>
       </c>
     </row>
     <row r="30">
@@ -9537,13 +10339,13 @@
         </is>
       </c>
       <c r="G30" s="31" t="n">
-        <v>0</v>
+        <v>-0.03942648623649692</v>
       </c>
       <c r="H30" s="31" t="n">
-        <v>0.1872340745006349</v>
+        <v>0.1404256066028353</v>
       </c>
       <c r="I30" s="31" t="n">
-        <v>-0.08674307663288039</v>
+        <v>-0.1227495881523997</v>
       </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
@@ -9551,13 +10353,13 @@
         </is>
       </c>
       <c r="L30" s="22" t="n">
-        <v>0.0380487069110087</v>
+        <v>0.03856289055351581</v>
       </c>
       <c r="M30" s="22" t="n">
-        <v>0.09773662167330821</v>
+        <v>0.09828037093178477</v>
       </c>
       <c r="N30" s="22" t="n">
-        <v>-0.05770128204100999</v>
+        <v>-0.05723452688404651</v>
       </c>
     </row>
     <row r="31">
@@ -9567,27 +10369,27 @@
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>-0.006597520932073331</v>
+        <v>-0.005654992260496705</v>
       </c>
       <c r="C31" s="22" t="n">
-        <v>0.003809520176478731</v>
+        <v>0.004761922927129847</v>
       </c>
       <c r="D31" s="22" t="n">
-        <v>-0.06394318404914523</v>
+        <v>-0.06305506427307406</v>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>QuantumScape (US)</t>
+          <t>Solid Power (US)</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>0</v>
+        <v>0.005050500185316276</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>0.03465987921512736</v>
+        <v>0.02051280044866699</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>-0.2019801866142278</v>
+        <v>-0.2008032120823259</v>
       </c>
       <c r="K31" s="26" t="inlineStr">
         <is>
@@ -9595,13 +10397,13 @@
         </is>
       </c>
       <c r="L31" s="28" t="n">
-        <v>0.02593224953386375</v>
+        <v>0.02651829625667401</v>
       </c>
       <c r="M31" s="28" t="n">
-        <v>0.05677865262673787</v>
+        <v>0.05738013268878905</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>-0.05176085119379503</v>
+        <v>-0.05121786899865549</v>
       </c>
     </row>
     <row r="32">
@@ -9611,27 +10413,27 @@
         </is>
       </c>
       <c r="B32" s="22" t="n">
-        <v>0.02071752543934546</v>
+        <v>0.0212227463120418</v>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.03377685857156965</v>
+        <v>0.03428854337529241</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>-0.09049970303413579</v>
+        <v>-0.0900495309519499</v>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>Solid Power (US)</t>
+          <t>QuantumScape (US)</t>
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>0</v>
+        <v>-0.0322580912339705</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>0.01538460033650035</v>
+        <v>0.001283726435276744</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>-0.204819272493955</v>
+        <v>-0.2277227825609421</v>
       </c>
     </row>
     <row r="33">
@@ -9641,13 +10443,13 @@
         </is>
       </c>
       <c r="B33" s="22" t="n">
-        <v>-0.007766494760103715</v>
+        <v>-0.005623971173393305</v>
       </c>
       <c r="C33" s="22" t="n">
-        <v>-0.00696869811472578</v>
+        <v>-0.004824451850721112</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>-0.1419638958960466</v>
+        <v>-0.1401111439162116</v>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
@@ -9655,13 +10457,13 @@
         </is>
       </c>
       <c r="G33" s="31" t="n">
-        <v>0</v>
+        <v>-0.01610020574797755</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>-0.04607508101959501</v>
+        <v>-0.06143346848330222</v>
       </c>
       <c r="I33" s="31" t="n">
-        <v>-0.2310866344905435</v>
+        <v>-0.2434662978776155</v>
       </c>
     </row>
     <row r="34">
@@ -9671,13 +10473,13 @@
         </is>
       </c>
       <c r="B34" s="22" t="n">
-        <v>0.00196179091342441</v>
+        <v>0.00490438374022184</v>
       </c>
       <c r="C34" s="22" t="n">
-        <v>-0.01731604591141167</v>
+        <v>-0.01443006884069542</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>-0.1448304383788255</v>
+        <v>-0.1423189495770141</v>
       </c>
       <c r="F34" s="26" t="inlineStr">
         <is>
@@ -9685,13 +10487,13 @@
         </is>
       </c>
       <c r="G34" s="28" t="n">
-        <v>0</v>
+        <v>-0.02068357075828217</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>0.0478008682581669</v>
+        <v>0.02519716625086921</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>-0.1811572925579017</v>
+        <v>-0.1986854701683208</v>
       </c>
     </row>
     <row r="35">
@@ -9701,13 +10503,13 @@
         </is>
       </c>
       <c r="B35" s="22" t="n">
-        <v>0.004030732843997242</v>
+        <v>0.005130061742459668</v>
       </c>
       <c r="C35" s="22" t="n">
-        <v>-0.01827302872339942</v>
+        <v>-0.01719812056110903</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>-0.1774242423027806</v>
+        <v>-0.1765235912848085</v>
       </c>
     </row>
     <row r="36">
@@ -9717,13 +10519,13 @@
         </is>
       </c>
       <c r="B36" s="22" t="n">
-        <v>0</v>
+        <v>0.02555171612093998</v>
       </c>
       <c r="C36" s="22" t="n">
-        <v>-0.1146530263296475</v>
+        <v>-0.09203089178988921</v>
       </c>
       <c r="D36" s="22" t="n">
-        <v>-0.2064516724458449</v>
+        <v>-0.1861751508519344</v>
       </c>
     </row>
     <row r="37">
@@ -9733,13 +10535,13 @@
         </is>
       </c>
       <c r="B37" s="31" t="n">
-        <v>-0.0217792598473473</v>
+        <v>-0.0214101114964611</v>
       </c>
       <c r="C37" s="31" t="n">
-        <v>-0.05961675965160362</v>
+        <v>-0.05926188992933468</v>
       </c>
       <c r="D37" s="31" t="n">
-        <v>-0.2508833922261484</v>
+        <v>-0.250600700243623</v>
       </c>
     </row>
     <row r="38">
@@ -9749,13 +10551,13 @@
         </is>
       </c>
       <c r="B38" s="28" t="n">
-        <v>0.00222377336577933</v>
+        <v>0.005951891068898152</v>
       </c>
       <c r="C38" s="28" t="n">
-        <v>-0.01479780543393807</v>
+        <v>-0.0114037806213367</v>
       </c>
       <c r="D38" s="28" t="n">
-        <v>-0.1243305394162092</v>
+        <v>-0.1213124952790635</v>
       </c>
     </row>
   </sheetData>
@@ -11048,10 +11850,10 @@
         <v>0.01425410405019512</v>
       </c>
       <c r="U17" s="22" t="n">
-        <v>-0.004080473764783432</v>
+        <v>-0.004251609381155023</v>
       </c>
       <c r="V17" s="22" t="n">
-        <v>-0.1026711546389685</v>
+        <v>-0.10139035457713</v>
       </c>
     </row>
     <row r="18">
@@ -11118,10 +11920,10 @@
         <v>-0.01591714674896998</v>
       </c>
       <c r="U18" s="22" t="n">
-        <v>0.0005521048999309766</v>
+        <v>0.005203475756635585</v>
       </c>
       <c r="V18" s="22" t="n">
-        <v>-0.07345166748503894</v>
+        <v>-0.06915510615984852</v>
       </c>
     </row>
     <row r="19">
@@ -11188,10 +11990,10 @@
         <v>0.03472147104242349</v>
       </c>
       <c r="U19" s="22" t="n">
-        <v>0.007870123020937203</v>
+        <v>0.005396120096030669</v>
       </c>
       <c r="V19" s="22" t="n">
-        <v>-0.1262606126614515</v>
+        <v>-0.1279185067089894</v>
       </c>
     </row>
     <row r="20">
@@ -11258,10 +12060,10 @@
         <v>0.006345338835901969</v>
       </c>
       <c r="U20" s="22" t="n">
-        <v>0.01795012256169864</v>
+        <v>0.01424052490168895</v>
       </c>
       <c r="V20" s="22" t="n">
-        <v>-0.2575651106648142</v>
+        <v>-0.2601927498556398</v>
       </c>
     </row>
     <row r="21">
@@ -11328,10 +12130,10 @@
         <v>0.04065104712189489</v>
       </c>
       <c r="U21" s="22" t="n">
-        <v>0.00222377336577933</v>
+        <v>0.005951891068898152</v>
       </c>
       <c r="V21" s="22" t="n">
-        <v>-0.1243305394162092</v>
+        <v>-0.1213124952790635</v>
       </c>
     </row>
     <row r="22">
@@ -11398,10 +12200,10 @@
         <v>0.09194888397223921</v>
       </c>
       <c r="U22" s="22" t="n">
-        <v>0.02593224953386375</v>
+        <v>0.02651829625667401</v>
       </c>
       <c r="V22" s="22" t="n">
-        <v>-0.05176085119379503</v>
+        <v>-0.05121786899865549</v>
       </c>
     </row>
     <row r="23">
@@ -11468,10 +12270,10 @@
         <v>0.006525467655148026</v>
       </c>
       <c r="U23" s="22" t="n">
-        <v>0</v>
+        <v>-0.02068357075828217</v>
       </c>
       <c r="V23" s="22" t="n">
-        <v>-0.1811572925579017</v>
+        <v>-0.1986854701683208</v>
       </c>
     </row>
   </sheetData>
@@ -12157,22 +12959,22 @@
         </is>
       </c>
       <c r="L5" s="21" t="n">
-        <v>4.98799991607666</v>
+        <v>4.986000061035156</v>
       </c>
       <c r="M5" s="21" t="n">
-        <v>0</v>
+        <v>-0.001999855041503906</v>
       </c>
       <c r="N5" s="21" t="n">
-        <v>-0.1480002403259277</v>
+        <v>-0.1500000953674316</v>
       </c>
       <c r="O5" s="21" t="n">
-        <v>-0.1960000991821289</v>
+        <v>-0.1979999542236328</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>0.3090000152587891</v>
+        <v>0.3070001602172852</v>
       </c>
       <c r="Q5" s="21" t="n">
-        <v>0.8249998092651367</v>
+        <v>0.8229999542236328</v>
       </c>
     </row>
     <row r="6">
@@ -12215,22 +13017,22 @@
         </is>
       </c>
       <c r="L6" s="21" t="n">
-        <v>1323.0400390625</v>
+        <v>1325.170043945312</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>-2.949951171875</v>
+        <v>-0.8199462890625</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>-10.3900146484375</v>
+        <v>-8.260009765625</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>-44.3199462890625</v>
+        <v>-42.18994140625</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>-151</v>
+        <v>-148.8699951171875</v>
       </c>
       <c r="Q6" s="21" t="n">
-        <v>-114.8699951171875</v>
+        <v>-112.739990234375</v>
       </c>
     </row>
     <row r="7">
@@ -12305,22 +13107,22 @@
         </is>
       </c>
       <c r="C9" s="21" t="n">
-        <v>25955.33984375</v>
+        <v>26169.380859375</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>0</v>
+        <v>0.008246511774205878</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>-0.01799223446523568</v>
+        <v>-0.009894095864391605</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-0.0411316394145832</v>
+        <v>-0.03322432018910204</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>0.03921871309907554</v>
+        <v>0.04778864245262215</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>0.1167434278223707</v>
+        <v>0.1259526656486749</v>
       </c>
     </row>
     <row r="10">
@@ -12335,22 +13137,22 @@
         </is>
       </c>
       <c r="C10" s="21" t="n">
-        <v>6992.35009765625</v>
+        <v>7019.19140625</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>0</v>
+        <v>0.003838667718131905</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>0.01549451163508397</v>
+        <v>0.01939265763483777</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.0129919495237073</v>
+        <v>-0.009203153582807655</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0.07667539991508598</v>
+        <v>0.08080839901564674</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>0.225180448970282</v>
+        <v>0.2298835096086307</v>
       </c>
     </row>
     <row r="11">
@@ -12365,22 +13167,22 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>7623.68017578125</v>
+        <v>7676.77001953125</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>0</v>
+        <v>0.006963807836358971</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-0.008718262747200667</v>
+        <v>-0.001815167217280034</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.01546217726463983</v>
+        <v>-0.008606045059483591</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>0.02856189518459984</v>
+        <v>0.0357246025704665</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0.1136776241006865</v>
+        <v>0.1214330610665766</v>
       </c>
     </row>
     <row r="12">
@@ -12425,22 +13227,22 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>48.15999984741211</v>
+        <v>48.72000122070312</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>0</v>
+        <v>0.01162793552876451</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0.01667724157358164</v>
+        <v>0.02849909899216141</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.09745128754610022</v>
+        <v>-0.08695650930611687</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.2737370562867087</v>
+        <v>0.2885479886578088</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0.6624094231583733</v>
+        <v>0.6817398127532694</v>
       </c>
     </row>
     <row r="14">
@@ -12455,22 +13257,22 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>149.5399932861328</v>
+        <v>150.4700012207031</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0</v>
+        <v>0.006219125159319772</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0.01136204970138244</v>
+        <v>0.01765183686986149</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.03541253651804332</v>
+        <v>-0.02941364635553811</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.006246693700790784</v>
+        <v>-6.641751142810737e-05</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>0.2264413426708163</v>
+        <v>0.2340687348814503</v>
       </c>
     </row>
     <row r="15">
@@ -12485,22 +13287,22 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>73.30000305175781</v>
+        <v>73.48999786376953</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>0</v>
+        <v>0.002592016427032995</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.0008178511190645166</v>
+        <v>0.001772045424432989</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.02630175026096826</v>
+        <v>-0.02377790840267147</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>-0.02123109027706038</v>
+        <v>-0.01869410518478942</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>0.03268525760921359</v>
+        <v>0.03536199476089141</v>
       </c>
     </row>
     <row r="16">
@@ -12515,22 +13317,22 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>118.9400024414062</v>
+        <v>119.7200012207031</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>0</v>
+        <v>0.006557917969449489</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>0.04296739290197382</v>
+        <v>0.04980708750943563</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>0.07618536060522119</v>
+        <v>0.08324289591999268</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.03714686191920258</v>
+        <v>0.04394838596194073</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>0.04296739290197382</v>
+        <v>0.04980708750943563</v>
       </c>
     </row>
     <row r="17">
@@ -12605,22 +13407,22 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>23199.2890625</v>
+        <v>23093.369140625</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>0.004586594586091453</v>
+        <v>0</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>-0.04082969998280794</v>
+        <v>-0.0452089394917834</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>-0.05348004799681505</v>
+        <v>-0.05780153039652192</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>-0.07066158398281719</v>
+        <v>-0.07490462143774901</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>-0.09485754451248185</v>
+        <v>-0.09899011158868398</v>
       </c>
     </row>
     <row r="20">
@@ -12635,22 +13437,22 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>68.72000122070312</v>
+        <v>68.98000335693359</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>-0.003769239251629197</v>
+        <v>0</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.008369434422989874</v>
+        <v>-0.004617600010568879</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.08029978455537745</v>
+        <v>-0.07682009863483663</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>0.002041402535878145</v>
+        <v>0.005832626351692127</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>0.123753562075525</v>
+        <v>0.1280052838675236</v>
       </c>
     </row>
     <row r="22">
@@ -13129,22 +13931,22 @@
         </is>
       </c>
       <c r="J33" s="22" t="n">
-        <v>0</v>
+        <v>0.008246511774205878</v>
       </c>
       <c r="K33" s="22" t="n">
-        <v>0</v>
+        <v>0.003838667718131905</v>
       </c>
       <c r="L33" s="22" t="n">
-        <v>0</v>
+        <v>0.006963807836358971</v>
       </c>
       <c r="M33" s="22" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="22" t="n">
-        <v>0</v>
+        <v>0.01162793552876451</v>
       </c>
       <c r="O33" s="22" t="n">
-        <v>0</v>
+        <v>0.006219125159319772</v>
       </c>
     </row>
     <row r="35">
@@ -13414,10 +14216,10 @@
         </is>
       </c>
       <c r="B46" s="22" t="n">
-        <v>0</v>
+        <v>0.002592016427032995</v>
       </c>
       <c r="C46" s="22" t="n">
-        <v>0</v>
+        <v>0.006557917969449489</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -13698,10 +14500,10 @@
         </is>
       </c>
       <c r="B59" s="22" t="n">
-        <v>0.004586594586091453</v>
+        <v>0</v>
       </c>
       <c r="C59" s="22" t="n">
-        <v>-0.003769239251629197</v>
+        <v>0</v>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
@@ -13709,10 +14511,10 @@
         </is>
       </c>
       <c r="J59" s="21" t="n">
-        <v>4.98799991607666</v>
+        <v>4.986000061035156</v>
       </c>
       <c r="K59" s="23" t="n">
-        <v>1323.0400390625</v>
+        <v>1325.170043945312</v>
       </c>
     </row>
     <row r="61">
@@ -17628,113 +18430,113 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>0</v>
+        <v>0.03445578383972414</v>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="E5" s="22" t="n">
-        <v>0</v>
+        <v>-0.01229172319094829</v>
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Xencor Inc</t>
         </is>
       </c>
       <c r="H5" s="22" t="n">
-        <v>0</v>
+        <v>0.1588562331819272</v>
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals Inc</t>
+          <t>Ocugen Inc</t>
         </is>
       </c>
       <c r="K5" s="22" t="n">
-        <v>0</v>
+        <v>-0.04270270009037358</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Idexx Laboratories</t>
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>0</v>
+        <v>0.01754169849778897</v>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Becton Dickinson</t>
         </is>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0</v>
+        <v>-0.01266906754846631</v>
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>Natera Inc</t>
+          <t>Oruka Therapeutics Inc</t>
         </is>
       </c>
       <c r="H6" s="22" t="n">
-        <v>0</v>
+        <v>0.127011854165578</v>
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t>Neurogene Inc</t>
+          <t>Tango Therapeutics Inc</t>
         </is>
       </c>
       <c r="K6" s="22" t="n">
-        <v>0</v>
+        <v>-0.04905743146007291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Gilead Sciences</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>0</v>
+        <v>0.01698288432000949</v>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>Align Technology</t>
         </is>
       </c>
       <c r="E7" s="22" t="n">
-        <v>0</v>
+        <v>-0.01456216477892924</v>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>Twist Bioscience Corp</t>
+          <t>Replimune Group Inc</t>
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>0</v>
+        <v>0.08813265493192346</v>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>Ovid Therapeutics Inc</t>
+          <t>Immunitybio Inc</t>
         </is>
       </c>
       <c r="K7" s="22" t="n">
-        <v>0</v>
+        <v>-0.04987838332485428</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Align Technology</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>0</v>
+        <v>0.01672839192628972</v>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
@@ -17742,227 +18544,227 @@
         </is>
       </c>
       <c r="E8" s="22" t="n">
-        <v>0</v>
+        <v>-0.01504462524945971</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>Halozyme Therapeutics Inc</t>
+          <t>Savara Inc</t>
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>0</v>
+        <v>0.07109009612563</v>
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t>Assembly Biosciences Inc</t>
+          <t>Inhibrx Biosciences Inc</t>
         </is>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0</v>
+        <v>-0.05108156760940374</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>0</v>
+        <v>0.01669844148232169</v>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="E9" s="22" t="n">
-        <v>0</v>
+        <v>-0.0176755822803446</v>
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Praxis Precision Medicines I</t>
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>0</v>
+        <v>0.0570446218832239</v>
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>Aura Biosciences Inc</t>
+          <t>Ideaya Biosciences Inc</t>
         </is>
       </c>
       <c r="K9" s="22" t="n">
-        <v>0</v>
+        <v>-0.05272250258214672</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Baxter International</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0</v>
+        <v>0.016428730527279</v>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="E10" s="22" t="n">
-        <v>0</v>
+        <v>-0.01961587599354675</v>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>Iovance Biotherapeutics Inc</t>
+          <t>Grail Inc</t>
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>0</v>
+        <v>0.05552621984835149</v>
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>Faeth Therapeutics Inc</t>
+          <t>Summit Therapeutics Inc</t>
         </is>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0</v>
+        <v>-0.0627020200572439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Becton Dickinson</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0</v>
+        <v>0.01611116197374129</v>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="E11" s="22" t="n">
-        <v>0</v>
+        <v>-0.02061848349826545</v>
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>Biogen Inc</t>
+          <t>Hemab Therapeutics Holdings</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0</v>
+        <v>0.04709299011705137</v>
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>Lexeo Therapeutics Inc</t>
+          <t>Cabaletta Bio Inc</t>
         </is>
       </c>
       <c r="K11" s="22" t="n">
-        <v>0</v>
+        <v>-0.0816326547162195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>0</v>
+        <v>0.01222509447207076</v>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="E12" s="22" t="n">
-        <v>0</v>
+        <v>-0.02074152229598425</v>
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Amgen Inc</t>
+          <t>Vir Biotechnology Inc</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0</v>
+        <v>0.04446549485322615</v>
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>Compass Therapeutics Inc</t>
+          <t>Climb Bio Inc</t>
         </is>
       </c>
       <c r="K12" s="22" t="n">
-        <v>0</v>
+        <v>-0.1354268123252163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>0</v>
+        <v>0.01137898109837687</v>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0</v>
+        <v>-0.03049735564330569</v>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Viridian Therapeutics Inc</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0</v>
+        <v>0.0433616127386669</v>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>Crescent Biopharma Inc</t>
+          <t>Arrivent Biopharma Inc</t>
         </is>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0</v>
+        <v>-0.2685714449201312</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>0.01071584043688989</v>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Merck &amp; Co.</t>
         </is>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0</v>
+        <v>-0.03207822348080414</v>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>Exelixis Inc</t>
+          <t>Disc Medicine Inc</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>0</v>
+        <v>0.04227622380307539</v>
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>Bridgebio Oncology Therapeut</t>
+          <t>Oric Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="K14" s="22" t="n">
-        <v>0</v>
+        <v>-0.3200455678185536</v>
       </c>
     </row>
     <row r="15">
@@ -17972,7 +18774,7 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>0</v>
+        <v>0.01692670085744918</v>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
@@ -17980,7 +18782,7 @@
         </is>
       </c>
       <c r="E15" s="28" t="n">
-        <v>0</v>
+        <v>-0.01957946239600544</v>
       </c>
       <c r="G15" s="26" t="inlineStr">
         <is>
@@ -17988,7 +18790,7 @@
         </is>
       </c>
       <c r="H15" s="28" t="n">
-        <v>0</v>
+        <v>0.07348580016486539</v>
       </c>
       <c r="J15" s="26" t="inlineStr">
         <is>
@@ -17996,7 +18798,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0</v>
+        <v>-0.1113821084904216</v>
       </c>
     </row>
     <row r="17">
@@ -18036,181 +18838,181 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>탠덤</t>
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>0.01097368714982605</v>
+        <v>0.08433730852649379</v>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>Cigna</t>
+          <t>인모드</t>
         </is>
       </c>
       <c r="E19" s="22" t="n">
-        <v>0</v>
+        <v>-0.01789548999437285</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Insilico</t>
+          <t>Twist</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>0.0084033529263976</v>
+        <v>0.03809320969700858</v>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>유나이티드</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>0</v>
+        <v>-0.01945395884142953</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>Genscript</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0.001898717253736804</v>
+        <v>0.03604862024404065</v>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>가던트</t>
+          <t>Elevance</t>
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0</v>
+        <v>-0.01961587599354675</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>우시 바이오</t>
+          <t>패썸 파마</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>0.001310073674465562</v>
+        <v>0.03484325680788913</v>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>일루미나</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>0</v>
+        <v>-0.02263374485596703</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>슈뢰딩거</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>0</v>
+        <v>0.0294117977049948</v>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>Twist</t>
+          <t>Akeso</t>
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>0</v>
+        <v>-0.02886836078579236</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Absci</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>0</v>
+        <v>0.0294117097073654</v>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>Merck &amp; Co</t>
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>-0.009549795361528002</v>
+        <v>-0.03207822348080414</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>가던트</t>
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>0</v>
+        <v>0.02466287037962056</v>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>우시 XDC</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="E25" s="22" t="n">
-        <v>-0.01332404680189281</v>
+        <v>-0.04104477611940294</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="B26" s="22" t="n">
-        <v>0</v>
+        <v>0.02282451386419293</v>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>Summit</t>
         </is>
       </c>
       <c r="E26" s="22" t="n">
-        <v>-0.02263374485596703</v>
+        <v>-0.0627020200572439</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Sandoz</t>
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>0</v>
+        <v>0.02107608320182575</v>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>Akeso</t>
+          <t>메타비아</t>
         </is>
       </c>
       <c r="E27" s="22" t="n">
-        <v>-0.03695146656611603</v>
+        <v>-0.1195651901617091</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>할로자임</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>0</v>
+        <v>0.01894449817281374</v>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>오릭 파마</t>
         </is>
       </c>
       <c r="E28" s="22" t="n">
-        <v>-0.04104477611940294</v>
+        <v>-0.3200455678185536</v>
       </c>
     </row>
     <row r="29">
@@ -18220,7 +19022,7 @@
         </is>
       </c>
       <c r="B29" s="28" t="n">
-        <v>0.002258583100442601</v>
+        <v>0.03396538683062453</v>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
@@ -18228,7 +19030,7 @@
         </is>
       </c>
       <c r="E29" s="28" t="n">
-        <v>-0.01235038297049068</v>
+        <v>-0.06839032081088223</v>
       </c>
     </row>
     <row r="31">
@@ -18338,17 +19140,17 @@
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="B33" s="31" t="n">
-        <v>0</v>
+        <v>0.004460331604580592</v>
       </c>
       <c r="C33" s="31" t="n">
-        <v>0.07052850581631187</v>
+        <v>0.03128178555664296</v>
       </c>
       <c r="D33" s="31" t="n">
-        <v>0.09899386159968504</v>
+        <v>0.09315124569323308</v>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
@@ -18356,13 +19158,13 @@
         </is>
       </c>
       <c r="G33" s="31" t="n">
-        <v>0</v>
+        <v>0.004748338173414135</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>0.03033264059958585</v>
+        <v>0.03522500840825948</v>
       </c>
       <c r="I33" s="31" t="n">
-        <v>0.1226012819768971</v>
+        <v>0.1279317724976317</v>
       </c>
       <c r="K33" s="29" t="inlineStr">
         <is>
@@ -18370,13 +19172,13 @@
         </is>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0</v>
+        <v>0.02107608320182575</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>0.05327764081353381</v>
+        <v>0.07547660800594258</v>
       </c>
       <c r="N33" s="31" t="n">
-        <v>0.139909570760314</v>
+        <v>0.1639343997162159</v>
       </c>
       <c r="P33" s="29" t="inlineStr">
         <is>
@@ -18384,203 +19186,203 @@
         </is>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0</v>
+        <v>0.006717894415912751</v>
       </c>
       <c r="R33" s="31" t="n">
-        <v>0.10474975917499</v>
+        <v>0.1121713514131326</v>
       </c>
       <c r="S33" s="31" t="n">
-        <v>0.1728951062979778</v>
+        <v>0.1807744917830283</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="B34" s="22" t="n">
-        <v>0</v>
+        <v>0.01780044023506133</v>
       </c>
       <c r="C34" s="22" t="n">
-        <v>0.02670235260482245</v>
+        <v>0.02403462505791887</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>0.08829707983288171</v>
+        <v>0.08868912009881069</v>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>Danaher</t>
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>-0.009549795361528002</v>
+        <v>0.01071584043688989</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>0.01751927119831809</v>
+        <v>0.03805199315431529</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>0.05094029571628744</v>
+        <v>0.05373379655159227</v>
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="L34" s="22" t="n">
-        <v>-0.02263374485596703</v>
+        <v>0.01611116197374129</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>-0.04137235116044402</v>
+        <v>0.001642972961087619</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.0646100460206136</v>
       </c>
       <c r="P34" s="20" t="inlineStr">
         <is>
-          <t>할로자임</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>0</v>
+        <v>0.03604862024404065</v>
       </c>
       <c r="R34" s="22" t="n">
-        <v>0.02555099798708538</v>
+        <v>-0.0004516815337632929</v>
       </c>
       <c r="S34" s="22" t="n">
-        <v>0.09120125293573977</v>
+        <v>0.1279305919556359</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B35" s="22" t="n">
-        <v>0</v>
+        <v>0.01222509447207076</v>
       </c>
       <c r="C35" s="22" t="n">
-        <v>0.01047128218957916</v>
+        <v>0.04633595879013819</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>0.07703338430528128</v>
+        <v>0.0838290158616426</v>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>0</v>
+        <v>-0.009549795361528002</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>0.02704632857600142</v>
+        <v>0.01751927119831809</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>0.04256186990807187</v>
+        <v>0.05094029571628744</v>
       </c>
       <c r="K35" s="20" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="L35" s="22" t="n">
-        <v>0</v>
+        <v>-0.02263374485596703</v>
       </c>
       <c r="M35" s="22" t="n">
-        <v>-0.01423878563104253</v>
+        <v>-0.04137235116044402</v>
       </c>
       <c r="N35" s="22" t="n">
-        <v>0.04772989989861531</v>
+        <v>0.06442577030812324</v>
       </c>
       <c r="P35" s="20" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>할로자임</t>
         </is>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>0</v>
+        <v>0.01894449817281374</v>
       </c>
       <c r="R35" s="22" t="n">
-        <v>-0.03523029813910306</v>
+        <v>0.04497954699457907</v>
       </c>
       <c r="S35" s="22" t="n">
-        <v>0.08868499983133282</v>
+        <v>0.111873513078153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="B36" s="22" t="n">
+        <v>0.003850915591400383</v>
+      </c>
+      <c r="C36" s="22" t="n">
+        <v>0.01436252180482533</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0.08118094895736117</v>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>써모피셔</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>0.016428730527279</v>
+      </c>
+      <c r="H36" s="22" t="n">
+        <v>0.008110350210520867</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>0.04004433325498336</v>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>Biocon</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="22" t="n">
-        <v>0.02004076568902735</v>
-      </c>
-      <c r="D36" s="22" t="n">
-        <v>0.0751879827613382</v>
-      </c>
-      <c r="F36" s="20" t="inlineStr">
-        <is>
-          <t>써모피셔</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="22" t="n">
-        <v>-0.008183928756562153</v>
-      </c>
-      <c r="I36" s="22" t="n">
-        <v>0.0232338992577017</v>
-      </c>
-      <c r="K36" s="20" t="inlineStr">
-        <is>
-          <t>Biocon</t>
-        </is>
-      </c>
-      <c r="L36" s="22" t="n">
-        <v>0.01097368714982605</v>
-      </c>
       <c r="M36" s="22" t="n">
-        <v>-0.03808827119715075</v>
+        <v>-0.04852941176470593</v>
       </c>
       <c r="N36" s="22" t="n">
-        <v>-0.1614102877103365</v>
+        <v>-0.1705128205128205</v>
       </c>
       <c r="P36" s="20" t="inlineStr">
         <is>
-          <t>오릭 파마</t>
+          <t>Xenon</t>
         </is>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>0</v>
+        <v>0.01216752414598665</v>
       </c>
       <c r="R36" s="22" t="n">
-        <v>0.03537734275301618</v>
+        <v>0.01966928707792026</v>
       </c>
       <c r="S36" s="22" t="n">
-        <v>-0.02444443879304103</v>
+        <v>-0.0849321995872242</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>0</v>
+        <v>-0.01945395884142953</v>
       </c>
       <c r="C37" s="22" t="n">
-        <v>0.03369889217759225</v>
+        <v>0.0497024883255841</v>
       </c>
       <c r="D37" s="22" t="n">
-        <v>0.07073912885642986</v>
+        <v>0.07761408024914096</v>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
@@ -18602,43 +19404,43 @@
         </is>
       </c>
       <c r="L37" s="31" t="n">
-        <v>0</v>
+        <v>0.008733616270600209</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>-0.08946327382348973</v>
+        <v>-0.08151099545677543</v>
       </c>
       <c r="N37" s="31" t="n">
-        <v>-0.2157534582124094</v>
+        <v>-0.2089041498548913</v>
       </c>
       <c r="P37" s="20" t="inlineStr">
         <is>
-          <t>Xenon</t>
+          <t>패썸 파마</t>
         </is>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>0</v>
+        <v>0.03484325680788913</v>
       </c>
       <c r="R37" s="22" t="n">
-        <v>0.007411582325034027</v>
+        <v>-0.1526391065228329</v>
       </c>
       <c r="S37" s="22" t="n">
-        <v>-0.09593246317119131</v>
+        <v>-0.2345360976778769</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B38" s="22" t="n">
-        <v>0</v>
+        <v>-0.007992000187495574</v>
       </c>
       <c r="C38" s="22" t="n">
-        <v>0.00612515437841421</v>
+        <v>0.01188859969838751</v>
       </c>
       <c r="D38" s="22" t="n">
-        <v>0.06964889880316583</v>
+        <v>0.0665950802015165</v>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
@@ -18646,13 +19448,13 @@
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>-0.01332404680189281</v>
+        <v>-0.01192154371856891</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>-0.05507049888761473</v>
+        <v>-0.05372733598338242</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>-0.1266294747510146</v>
+        <v>-0.1253880288126844</v>
       </c>
       <c r="K38" s="26" t="inlineStr">
         <is>
@@ -18660,27 +19462,27 @@
         </is>
       </c>
       <c r="L38" s="28" t="n">
-        <v>-0.002332011541228196</v>
+        <v>0.004657423318040044</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>-0.02597700819971864</v>
+        <v>-0.01885863548297904</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>-0.02501970099113868</v>
+        <v>-0.01728935086455179</v>
       </c>
       <c r="P38" s="20" t="inlineStr">
         <is>
-          <t>메타비아</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>0</v>
+        <v>-0.01162791689555986</v>
       </c>
       <c r="R38" s="22" t="n">
-        <v>0.1219511982374859</v>
+        <v>-0.005400492150899661</v>
       </c>
       <c r="S38" s="22" t="n">
-        <v>-0.178571405763528</v>
+        <v>-0.2523680385403156</v>
       </c>
     </row>
     <row r="39">
@@ -18690,13 +19492,13 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0</v>
+        <v>0.003323762593572255</v>
       </c>
       <c r="C39" s="22" t="n">
-        <v>0.04598968396017833</v>
+        <v>0.04946630534498775</v>
       </c>
       <c r="D39" s="22" t="n">
-        <v>0.01853067925674634</v>
+        <v>0.02191603342886572</v>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
@@ -18704,27 +19506,27 @@
         </is>
       </c>
       <c r="G39" s="31" t="n">
-        <v>0.001310073674465562</v>
+        <v>0.002183456124109195</v>
       </c>
       <c r="H39" s="31" t="n">
-        <v>-0.04854772023960419</v>
+        <v>-0.04771782573972483</v>
       </c>
       <c r="I39" s="31" t="n">
-        <v>-0.1289648759495263</v>
+        <v>-0.1282051244895442</v>
       </c>
       <c r="P39" s="20" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>메타비아</t>
         </is>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>0</v>
+        <v>-0.1195651901617091</v>
       </c>
       <c r="R39" s="22" t="n">
-        <v>0.006300688628416262</v>
+        <v>-0.01219511013193653</v>
       </c>
       <c r="S39" s="22" t="n">
-        <v>-0.2435723608143604</v>
+        <v>-0.2767856718376772</v>
       </c>
     </row>
     <row r="40">
@@ -18734,13 +19536,13 @@
         </is>
       </c>
       <c r="B40" s="22" t="n">
-        <v>0</v>
+        <v>0.006896521657558496</v>
       </c>
       <c r="C40" s="22" t="n">
-        <v>0.02608170116065223</v>
+        <v>0.03315809583513096</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>0.0005914585681168205</v>
+        <v>0.007492059232499848</v>
       </c>
       <c r="F40" s="26" t="inlineStr">
         <is>
@@ -18748,13 +19550,13 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>-0.003080538355565036</v>
+        <v>0.001800718025942188</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>-0.006384050988799873</v>
+        <v>-0.001474712594773846</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>-0.003434493321900886</v>
+        <v>0.001610370758077525</v>
       </c>
       <c r="K40" s="19" t="inlineStr">
         <is>
@@ -18763,17 +19565,17 @@
       </c>
       <c r="P40" s="20" t="inlineStr">
         <is>
-          <t>패썸 파마</t>
+          <t>Axsome</t>
         </is>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>0</v>
+        <v>-0.006756727612402313</v>
       </c>
       <c r="R40" s="22" t="n">
-        <v>-0.1811698168754909</v>
+        <v>-0.07541236239081073</v>
       </c>
       <c r="S40" s="22" t="n">
-        <v>-0.2603093296628344</v>
+        <v>-0.2906942726275965</v>
       </c>
     </row>
     <row r="41">
@@ -18783,13 +19585,13 @@
         </is>
       </c>
       <c r="B41" s="22" t="n">
-        <v>0</v>
+        <v>0.002048702499813704</v>
       </c>
       <c r="C41" s="22" t="n">
-        <v>0.01639773810880762</v>
+        <v>0.01848003469567616</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>-0.008883306478769226</v>
+        <v>-0.006852803231145232</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -18813,17 +19615,17 @@
       </c>
       <c r="P41" s="20" t="inlineStr">
         <is>
-          <t>Axsome</t>
+          <t>오릭 파마</t>
         </is>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>0</v>
+        <v>-0.3200455678185536</v>
       </c>
       <c r="R41" s="22" t="n">
-        <v>-0.06912267788471516</v>
+        <v>-0.295990586814838</v>
       </c>
       <c r="S41" s="22" t="n">
-        <v>-0.285869084552321</v>
+        <v>-0.33666667231807</v>
       </c>
     </row>
     <row r="42">
@@ -18833,13 +19635,13 @@
         </is>
       </c>
       <c r="B42" s="22" t="n">
-        <v>0</v>
+        <v>0.009438574191343641</v>
       </c>
       <c r="C42" s="22" t="n">
-        <v>0.03948147892956522</v>
+        <v>0.04929270198896951</v>
       </c>
       <c r="D42" s="22" t="n">
-        <v>-0.01998590153430213</v>
+        <v>-0.01073596575737079</v>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
@@ -18852,13 +19654,13 @@
         </is>
       </c>
       <c r="L42" s="31" t="n">
-        <v>0</v>
+        <v>0.0114138798110015</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>-0.03267239134839062</v>
+        <v>-0.02163143028537773</v>
       </c>
       <c r="N42" s="31" t="n">
-        <v>-0.06163933759178619</v>
+        <v>-0.05092900177168713</v>
       </c>
       <c r="P42" s="29" t="inlineStr">
         <is>
@@ -18866,13 +19668,13 @@
         </is>
       </c>
       <c r="Q42" s="31" t="n">
-        <v>0</v>
+        <v>0.005882394190066309</v>
       </c>
       <c r="R42" s="31" t="n">
-        <v>-0.03225807910990874</v>
+        <v>-0.02656543965698122</v>
       </c>
       <c r="S42" s="31" t="n">
-        <v>-0.4687500310440846</v>
+        <v>-0.4656250093132254</v>
       </c>
     </row>
     <row r="43">
@@ -18882,13 +19684,13 @@
         </is>
       </c>
       <c r="B43" s="22" t="n">
-        <v>0</v>
+        <v>0.004567366547487905</v>
       </c>
       <c r="C43" s="22" t="n">
-        <v>0.05130146057500218</v>
+        <v>0.0561031396973577</v>
       </c>
       <c r="D43" s="22" t="n">
-        <v>-0.02140672508451158</v>
+        <v>-0.01693713089706594</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -18916,13 +19718,13 @@
         </is>
       </c>
       <c r="L43" s="22" t="n">
-        <v>0</v>
+        <v>0.00640207312435237</v>
       </c>
       <c r="M43" s="22" t="n">
-        <v>0.025607377218968</v>
+        <v>0.03217339064479918</v>
       </c>
       <c r="N43" s="22" t="n">
-        <v>-0.08868142113280042</v>
+        <v>-0.08284709295131165</v>
       </c>
       <c r="P43" s="26" t="inlineStr">
         <is>
@@ -18930,13 +19732,13 @@
         </is>
       </c>
       <c r="Q43" s="28" t="n">
-        <v>0</v>
+        <v>-0.03433912145115157</v>
       </c>
       <c r="R43" s="28" t="n">
-        <v>-0.001643930290319018</v>
+        <v>-0.03918345937164304</v>
       </c>
       <c r="S43" s="28" t="n">
-        <v>-0.120466775473631</v>
+        <v>-0.1521029365085169</v>
       </c>
     </row>
     <row r="44">
@@ -18946,13 +19748,13 @@
         </is>
       </c>
       <c r="B44" s="31" t="n">
-        <v>0</v>
+        <v>-0.03207822348080414</v>
       </c>
       <c r="C44" s="31" t="n">
-        <v>0.01141822275217841</v>
+        <v>-0.02102627702982363</v>
       </c>
       <c r="D44" s="31" t="n">
-        <v>-0.03737326388432483</v>
+        <v>-0.06825261945404049</v>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
@@ -18960,13 +19762,13 @@
         </is>
       </c>
       <c r="G44" s="31" t="n">
-        <v>0</v>
+        <v>-0.00880096922122775</v>
       </c>
       <c r="H44" s="31" t="n">
-        <v>0.328947447673767</v>
+        <v>0.3172514220901612</v>
       </c>
       <c r="I44" s="31" t="n">
-        <v>0.2772834295411299</v>
+        <v>0.2660420973909543</v>
       </c>
       <c r="K44" s="20" t="inlineStr">
         <is>
@@ -18974,13 +19776,13 @@
         </is>
       </c>
       <c r="L44" s="22" t="n">
-        <v>0</v>
+        <v>0.01620320895679961</v>
       </c>
       <c r="M44" s="22" t="n">
-        <v>-0.03969306345462686</v>
+        <v>-0.02413300949911812</v>
       </c>
       <c r="N44" s="22" t="n">
-        <v>-0.1097555962133221</v>
+        <v>-0.09533078011614504</v>
       </c>
     </row>
     <row r="45">
@@ -18990,13 +19792,13 @@
         </is>
       </c>
       <c r="B45" s="28" t="n">
-        <v>0</v>
+        <v>0.0004239605735966527</v>
       </c>
       <c r="C45" s="28" t="n">
-        <v>0.02985310319517761</v>
+        <v>0.03025666498048295</v>
       </c>
       <c r="D45" s="28" t="n">
-        <v>0.03428110641681145</v>
+        <v>0.03480742203195401</v>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
@@ -19004,13 +19806,13 @@
         </is>
       </c>
       <c r="G45" s="22" t="n">
-        <v>0</v>
+        <v>0.009438574191343641</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>0.03948147892956522</v>
+        <v>0.04929270198896951</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>-0.01998590153430213</v>
+        <v>-0.01073596575737079</v>
       </c>
       <c r="K45" s="20" t="inlineStr">
         <is>
@@ -19018,13 +19820,13 @@
         </is>
       </c>
       <c r="L45" s="22" t="n">
-        <v>0</v>
+        <v>0.01654600270421391</v>
       </c>
       <c r="M45" s="22" t="n">
-        <v>0.01380396508555481</v>
+        <v>0.03057836823340332</v>
       </c>
       <c r="N45" s="22" t="n">
-        <v>-0.1925967163239102</v>
+        <v>-0.1792374194088143</v>
       </c>
       <c r="P45" s="19" t="inlineStr">
         <is>
@@ -19039,13 +19841,13 @@
         </is>
       </c>
       <c r="G46" s="22" t="n">
-        <v>0</v>
+        <v>-0.005007410870286999</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>0.05825393659428824</v>
+        <v>0.05295482432866216</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>-0.09346949334530663</v>
+        <v>-0.09800886405857612</v>
       </c>
       <c r="K46" s="29" t="inlineStr">
         <is>
@@ -19053,13 +19855,13 @@
         </is>
       </c>
       <c r="L46" s="31" t="n">
-        <v>0</v>
+        <v>0.009433953069178047</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>0.003154571048133104</v>
+        <v>0.01261828419253264</v>
       </c>
       <c r="N46" s="31" t="n">
-        <v>-0.2689654858680262</v>
+        <v>-0.2620689405697557</v>
       </c>
       <c r="P46" s="5" t="inlineStr">
         <is>
@@ -19108,27 +19910,27 @@
         </is>
       </c>
       <c r="L47" s="28" t="n">
+        <v>0.01199982353310909</v>
+      </c>
+      <c r="M47" s="28" t="n">
+        <v>0.005921120657247858</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>-0.1340826469635428</v>
+      </c>
+      <c r="P47" s="20" t="inlineStr">
+        <is>
+          <t>Lantheus</t>
+        </is>
+      </c>
+      <c r="Q47" s="22" t="n">
+        <v>0.001202355846875669</v>
+      </c>
+      <c r="R47" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M47" s="28" t="n">
-        <v>-0.005959908290072313</v>
-      </c>
-      <c r="N47" s="28" t="n">
-        <v>-0.144327711425969</v>
-      </c>
-      <c r="P47" s="20" t="inlineStr">
-        <is>
-          <t>Lantheus</t>
-        </is>
-      </c>
-      <c r="Q47" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="22" t="n">
-        <v>-0.001200911923403103</v>
-      </c>
       <c r="S47" s="22" t="n">
-        <v>-0.001999969482421871</v>
+        <v>-0.0008000183105468794</v>
       </c>
     </row>
     <row r="48">
@@ -19158,13 +19960,13 @@
         </is>
       </c>
       <c r="G48" s="31" t="n">
-        <v>0</v>
+        <v>-0.008447721661639762</v>
       </c>
       <c r="H48" s="31" t="n">
-        <v>0.02860242520545264</v>
+        <v>0.01991307821682931</v>
       </c>
       <c r="I48" s="31" t="n">
-        <v>-0.238133570664989</v>
+        <v>-0.2445696062033584</v>
       </c>
       <c r="P48" s="20" t="inlineStr">
         <is>
@@ -19172,13 +19974,13 @@
         </is>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>0</v>
+        <v>-0.01748632285055873</v>
       </c>
       <c r="R48" s="22" t="n">
-        <v>-0.148044710099873</v>
+        <v>-0.162942275353308</v>
       </c>
       <c r="S48" s="22" t="n">
-        <v>-0.2343096431318729</v>
+        <v>-0.2476987519156285</v>
       </c>
     </row>
     <row r="49">
@@ -19188,13 +19990,13 @@
         </is>
       </c>
       <c r="B49" s="31" t="n">
-        <v>0</v>
+        <v>-0.01634882287487849</v>
       </c>
       <c r="C49" s="31" t="n">
-        <v>-0.04177541791104977</v>
+        <v>-0.05744126187797649</v>
       </c>
       <c r="D49" s="31" t="n">
-        <v>0.03672319656547929</v>
+        <v>0.0197739926545526</v>
       </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
@@ -19202,13 +20004,13 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>-0.008208955223880588</v>
+        <v>-0.01077246073624276</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>0.06911710386999108</v>
+        <v>0.06594245151430089</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>-0.04707002994280454</v>
+        <v>-0.04966339046778119</v>
       </c>
       <c r="K49" s="19" t="inlineStr">
         <is>
@@ -19221,13 +20023,13 @@
         </is>
       </c>
       <c r="Q49" s="28" t="n">
-        <v>0</v>
+        <v>-0.008141983501841532</v>
       </c>
       <c r="R49" s="28" t="n">
-        <v>-0.07462281101163803</v>
+        <v>-0.08147113767665398</v>
       </c>
       <c r="S49" s="28" t="n">
-        <v>-0.1181548063071474</v>
+        <v>-0.1242493851130877</v>
       </c>
     </row>
     <row r="50">
@@ -19237,13 +20039,13 @@
         </is>
       </c>
       <c r="B50" s="22" t="n">
-        <v>0</v>
+        <v>0.004460320300152976</v>
       </c>
       <c r="C50" s="22" t="n">
-        <v>-0.03195163108780641</v>
+        <v>-0.02763382529641734</v>
       </c>
       <c r="D50" s="22" t="n">
-        <v>-0.1166272333471287</v>
+        <v>-0.1126871078634245</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -19273,13 +20075,13 @@
         </is>
       </c>
       <c r="B51" s="22" t="n">
-        <v>0</v>
+        <v>-0.007693886876112832</v>
       </c>
       <c r="C51" s="22" t="n">
-        <v>-0.01298963856887558</v>
+        <v>-0.02058358463527787</v>
       </c>
       <c r="D51" s="22" t="n">
-        <v>-0.1633067861934193</v>
+        <v>-0.1697442091304584</v>
       </c>
       <c r="F51" s="19" t="inlineStr">
         <is>
@@ -19288,17 +20090,17 @@
       </c>
       <c r="K51" s="20" t="inlineStr">
         <is>
-          <t>Summit</t>
+          <t>Akeso</t>
         </is>
       </c>
       <c r="L51" s="22" t="n">
-        <v>0</v>
+        <v>-0.02886836078579236</v>
       </c>
       <c r="M51" s="22" t="n">
-        <v>-0.006422570954105589</v>
+        <v>-0.07886094564044044</v>
       </c>
       <c r="N51" s="22" t="n">
-        <v>-0.09637853337152491</v>
+        <v>-0.1230448682378128</v>
       </c>
       <c r="P51" s="19" t="inlineStr">
         <is>
@@ -19343,17 +20145,17 @@
       </c>
       <c r="K52" s="20" t="inlineStr">
         <is>
-          <t>Akeso</t>
+          <t>Summit</t>
         </is>
       </c>
       <c r="L52" s="22" t="n">
-        <v>-0.03695146656611603</v>
+        <v>-0.0627020200572439</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.08652794372197781</v>
+        <v>-0.06872188283856606</v>
       </c>
       <c r="N52" s="22" t="n">
-        <v>-0.1303441063723741</v>
+        <v>-0.1530374246962196</v>
       </c>
       <c r="P52" s="5" t="inlineStr">
         <is>
@@ -19383,27 +20185,27 @@
         </is>
       </c>
       <c r="B53" s="28" t="n">
-        <v>0</v>
+        <v>-0.004895597362709586</v>
       </c>
       <c r="C53" s="28" t="n">
-        <v>-0.02374528555887362</v>
+        <v>-0.0284807816193586</v>
       </c>
       <c r="D53" s="28" t="n">
-        <v>-0.1053232508927331</v>
+        <v>-0.1101848762337985</v>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t>로슈</t>
+          <t>릴리</t>
         </is>
       </c>
       <c r="G53" s="31" t="n">
-        <v>0</v>
+        <v>0.004460331604580592</v>
       </c>
       <c r="H53" s="31" t="n">
-        <v>0.07052850581631187</v>
+        <v>0.03128178555664296</v>
       </c>
       <c r="I53" s="31" t="n">
-        <v>0.09899386159968504</v>
+        <v>0.09315124569323308</v>
       </c>
       <c r="K53" s="26" t="inlineStr">
         <is>
@@ -19411,13 +20213,13 @@
         </is>
       </c>
       <c r="L53" s="28" t="n">
-        <v>-0.01847573328305802</v>
+        <v>-0.04578519042151813</v>
       </c>
       <c r="M53" s="28" t="n">
-        <v>-0.0464752573380417</v>
+        <v>-0.07379141423950325</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>-0.1133613198719495</v>
+        <v>-0.1380411464670162</v>
       </c>
       <c r="P53" s="29" t="inlineStr">
         <is>
@@ -19425,29 +20227,29 @@
         </is>
       </c>
       <c r="Q53" s="31" t="n">
-        <v>0</v>
+        <v>-0.003320817300799361</v>
       </c>
       <c r="R53" s="31" t="n">
-        <v>0.03091223528095854</v>
+        <v>0.02748876409443191</v>
       </c>
       <c r="S53" s="31" t="n">
-        <v>0.1165436692914661</v>
+        <v>0.112835831757385</v>
       </c>
     </row>
     <row r="54">
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>릴리</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="G54" s="22" t="n">
-        <v>0</v>
+        <v>0.01222509447207076</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>0.02670235260482245</v>
+        <v>0.04633595879013819</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>0.08829707983288171</v>
+        <v>0.0838290158616426</v>
       </c>
       <c r="P54" s="20" t="inlineStr">
         <is>
@@ -19455,13 +20257,13 @@
         </is>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>0</v>
+        <v>-0.006498299159255261</v>
       </c>
       <c r="R54" s="22" t="n">
-        <v>0.0284575521674364</v>
+        <v>0.02177432732085705</v>
       </c>
       <c r="S54" s="22" t="n">
-        <v>0.05111829008090418</v>
+        <v>0.04428780898019369</v>
       </c>
     </row>
     <row r="55">
@@ -19472,17 +20274,17 @@
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>로슈</t>
         </is>
       </c>
       <c r="G55" s="22" t="n">
-        <v>0</v>
+        <v>-0.01945395884142953</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>0.03369889217759225</v>
+        <v>0.0497024883255841</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>0.07073912885642986</v>
+        <v>0.07761408024914096</v>
       </c>
       <c r="K55" s="19" t="inlineStr">
         <is>
@@ -19495,13 +20297,13 @@
         </is>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>0</v>
+        <v>-0.002407458939821416</v>
       </c>
       <c r="R55" s="22" t="n">
-        <v>0.01420642398417482</v>
+        <v>0.01176476366193002</v>
       </c>
       <c r="S55" s="22" t="n">
-        <v>0.01714159592944942</v>
+        <v>0.0146928693012649</v>
       </c>
     </row>
     <row r="56">
@@ -19531,13 +20333,13 @@
         </is>
       </c>
       <c r="G56" s="22" t="n">
-        <v>0</v>
+        <v>-0.006225674811762505</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>0.1242344740490458</v>
+        <v>0.1172353558014436</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>0.004691197794812751</v>
+        <v>-0.001563682888897966</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -19565,13 +20367,13 @@
         </is>
       </c>
       <c r="Q56" s="31" t="n">
-        <v>0</v>
+        <v>0.01137898109837687</v>
       </c>
       <c r="R56" s="31" t="n">
-        <v>-0.003459548518140787</v>
+        <v>0.00788006644303918</v>
       </c>
       <c r="S56" s="31" t="n">
-        <v>9.638833639313837e-05</v>
+        <v>0.01147646623582799</v>
       </c>
     </row>
     <row r="57">
@@ -19581,13 +20383,13 @@
         </is>
       </c>
       <c r="B57" s="22" t="n">
-        <v>0</v>
+        <v>-0.01136358710359819</v>
       </c>
       <c r="C57" s="22" t="n">
-        <v>0.03758290109600959</v>
+        <v>0.02579223742220105</v>
       </c>
       <c r="D57" s="22" t="n">
-        <v>0.04873370970487678</v>
+        <v>0.03681633284616592</v>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
@@ -19595,27 +20397,27 @@
         </is>
       </c>
       <c r="G57" s="22" t="n">
-        <v>0</v>
+        <v>0.002048702499813704</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>0.01639773810880762</v>
+        <v>0.01848003469567616</v>
       </c>
       <c r="I57" s="22" t="n">
-        <v>-0.008883306478769226</v>
+        <v>-0.006852803231145232</v>
       </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
-          <t>인슐렛</t>
+          <t>탠덤</t>
         </is>
       </c>
       <c r="L57" s="22" t="n">
-        <v>0</v>
+        <v>0.08433730852649379</v>
       </c>
       <c r="M57" s="22" t="n">
-        <v>0.04966178824701384</v>
+        <v>0.1538461896750021</v>
       </c>
       <c r="N57" s="22" t="n">
-        <v>0.06909161491363203</v>
+        <v>0.07999997820172999</v>
       </c>
       <c r="P57" s="26" t="inlineStr">
         <is>
@@ -19623,13 +20425,13 @@
         </is>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>0</v>
+        <v>-0.0002118985753747915</v>
       </c>
       <c r="R57" s="28" t="n">
-        <v>0.01752916572860724</v>
+        <v>0.01722698038006454</v>
       </c>
       <c r="S57" s="28" t="n">
-        <v>0.04622498590955321</v>
+        <v>0.04582324406866789</v>
       </c>
     </row>
     <row r="58">
@@ -19639,13 +20441,13 @@
         </is>
       </c>
       <c r="B58" s="22" t="n">
-        <v>0</v>
+        <v>-0.01152912036118636</v>
       </c>
       <c r="C58" s="22" t="n">
-        <v>0.06368328557712033</v>
+        <v>0.05141995295151935</v>
       </c>
       <c r="D58" s="22" t="n">
-        <v>0.01042301897307074</v>
+        <v>-0.001226269628383125</v>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
@@ -19653,27 +20455,27 @@
         </is>
       </c>
       <c r="G58" s="22" t="n">
-        <v>0</v>
+        <v>0.008060059134836761</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>-0.02874143060406154</v>
+        <v>-0.02091302909951331</v>
       </c>
       <c r="I58" s="22" t="n">
-        <v>-0.1630399631269226</v>
+        <v>-0.1562940157362305</v>
       </c>
       <c r="K58" s="20" t="inlineStr">
         <is>
-          <t>탠덤</t>
+          <t>인슐렛</t>
         </is>
       </c>
       <c r="L58" s="22" t="n">
-        <v>0</v>
+        <v>0.001677739810858947</v>
       </c>
       <c r="M58" s="22" t="n">
-        <v>0.06410263725312904</v>
+        <v>0.05142284761709348</v>
       </c>
       <c r="N58" s="22" t="n">
-        <v>-0.003999982561383897</v>
+        <v>0.07088527247742826</v>
       </c>
     </row>
     <row r="59">
@@ -19683,13 +20485,13 @@
         </is>
       </c>
       <c r="B59" s="22" t="n">
-        <v>0</v>
+        <v>-0.01456216477892924</v>
       </c>
       <c r="C59" s="22" t="n">
-        <v>0.03697982890493923</v>
+        <v>0.02187915776399962</v>
       </c>
       <c r="D59" s="22" t="n">
-        <v>0.007958779268949723</v>
+        <v>-0.0067192825651331</v>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
@@ -19697,13 +20499,13 @@
         </is>
       </c>
       <c r="G59" s="22" t="n">
-        <v>0</v>
+        <v>-0.007786907255249442</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>-0.02594808935437498</v>
+        <v>-0.03353294124437101</v>
       </c>
       <c r="I59" s="22" t="n">
-        <v>-0.4026927654847299</v>
+        <v>-0.4073439415227899</v>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
@@ -19711,13 +20513,13 @@
         </is>
       </c>
       <c r="L59" s="22" t="n">
-        <v>0</v>
+        <v>0.008083105384703915</v>
       </c>
       <c r="M59" s="22" t="n">
-        <v>-0.09351012562944938</v>
+        <v>-0.08618287244474521</v>
       </c>
       <c r="N59" s="22" t="n">
-        <v>-0.1294537752252346</v>
+        <v>-0.122417058348124</v>
       </c>
       <c r="P59" s="19" t="inlineStr">
         <is>
@@ -19732,13 +20534,13 @@
         </is>
       </c>
       <c r="B60" s="28" t="n">
-        <v>0</v>
+        <v>-0.01248495741457127</v>
       </c>
       <c r="C60" s="28" t="n">
-        <v>0.04608200519268971</v>
+        <v>0.03303044937924001</v>
       </c>
       <c r="D60" s="28" t="n">
-        <v>0.02237183598229908</v>
+        <v>0.009623593550883233</v>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
@@ -19746,13 +20548,13 @@
         </is>
       </c>
       <c r="G60" s="31" t="n">
-        <v>0</v>
+        <v>-0.004247293549768383</v>
       </c>
       <c r="H60" s="31" t="n">
-        <v>-0.03725577856869822</v>
+        <v>-0.04134483589046012</v>
       </c>
       <c r="I60" s="31" t="n">
-        <v>-0.4259008230382498</v>
+        <v>-0.4283391907694868</v>
       </c>
       <c r="K60" s="26" t="inlineStr">
         <is>
@@ -19760,13 +20562,13 @@
         </is>
       </c>
       <c r="L60" s="28" t="n">
-        <v>0</v>
+        <v>0.03136605124068555</v>
       </c>
       <c r="M60" s="28" t="n">
-        <v>0.006751433290231164</v>
+        <v>0.03969538828245012</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>-0.02145404762432883</v>
+        <v>0.009489397443678086</v>
       </c>
       <c r="P60" s="5" t="inlineStr">
         <is>
@@ -19796,13 +20598,13 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>0</v>
+        <v>-0.001364955843363505</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>0.02245208302868065</v>
+        <v>0.02090560211689257</v>
       </c>
       <c r="I61" s="28" t="n">
-        <v>-0.09222444875560776</v>
+        <v>-0.09322491154306671</v>
       </c>
       <c r="P61" s="20" t="inlineStr">
         <is>
@@ -19810,13 +20612,13 @@
         </is>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>0</v>
+        <v>0.001984147207757525</v>
       </c>
       <c r="R61" s="22" t="n">
-        <v>0.01886794586872376</v>
+        <v>0.02088952985859294</v>
       </c>
       <c r="S61" s="22" t="n">
-        <v>0.003984002791568075</v>
+        <v>0.005976054847340206</v>
       </c>
     </row>
     <row r="62">
@@ -19836,13 +20638,13 @@
         </is>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>0</v>
+        <v>-0.01789548999437285</v>
       </c>
       <c r="R62" s="22" t="n">
-        <v>-0.007107280025897666</v>
+        <v>-0.02487558176167981</v>
       </c>
       <c r="S62" s="22" t="n">
-        <v>-0.03321796183890324</v>
+        <v>-0.05051900012955446</v>
       </c>
     </row>
     <row r="63">
@@ -19897,13 +20699,13 @@
         </is>
       </c>
       <c r="Q63" s="22" t="n">
-        <v>0</v>
+        <v>0.02282451386419293</v>
       </c>
       <c r="R63" s="22" t="n">
-        <v>-0.04755433400589404</v>
+        <v>-0.02581522469752096</v>
       </c>
       <c r="S63" s="22" t="n">
-        <v>-0.1503030025597775</v>
+        <v>-0.13090908166134</v>
       </c>
     </row>
     <row r="64">
@@ -19913,13 +20715,13 @@
         </is>
       </c>
       <c r="B64" s="22" t="n">
-        <v>0</v>
+        <v>-0.001688277201613686</v>
       </c>
       <c r="C64" s="22" t="n">
-        <v>0.08485966838914161</v>
+        <v>0.08302812454404984</v>
       </c>
       <c r="D64" s="22" t="n">
-        <v>0.2039295516399773</v>
+        <v>0.2018969848255945</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -19947,13 +20749,13 @@
         </is>
       </c>
       <c r="L64" s="22" t="n">
-        <v>0</v>
+        <v>-0.001459248821862547</v>
       </c>
       <c r="M64" s="22" t="n">
-        <v>0.04411564751893726</v>
+        <v>0.0425920229904071</v>
       </c>
       <c r="N64" s="22" t="n">
-        <v>0.1248477024154722</v>
+        <v>0.1232062697309475</v>
       </c>
       <c r="P64" s="26" t="inlineStr">
         <is>
@@ -19961,13 +20763,13 @@
         </is>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0</v>
+        <v>0.002304390359192535</v>
       </c>
       <c r="R64" s="28" t="n">
-        <v>-0.01193122272102265</v>
+        <v>-0.009933758866869277</v>
       </c>
       <c r="S64" s="28" t="n">
-        <v>-0.05984565386903754</v>
+        <v>-0.05848400898118474</v>
       </c>
     </row>
     <row r="65">
@@ -19977,13 +20779,13 @@
         </is>
       </c>
       <c r="B65" s="22" t="n">
-        <v>0</v>
+        <v>-0.00256520321893694</v>
       </c>
       <c r="C65" s="22" t="n">
-        <v>0.06109180528233771</v>
+        <v>0.05836988916783992</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>0.06982774945527592</v>
+        <v>0.06708342386866506</v>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
@@ -19991,13 +20793,13 @@
         </is>
       </c>
       <c r="G65" s="22" t="n">
-        <v>0</v>
+        <v>0.01027234349990547</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>0.02022914588711844</v>
+        <v>0.03070929012228607</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>0.1183542684760066</v>
+        <v>0.1298423876763775</v>
       </c>
       <c r="K65" s="26" t="inlineStr">
         <is>
@@ -20005,13 +20807,13 @@
         </is>
       </c>
       <c r="L65" s="28" t="n">
-        <v>0</v>
+        <v>-0.001459248821862547</v>
       </c>
       <c r="M65" s="28" t="n">
-        <v>0.04411564751893726</v>
+        <v>0.0425920229904071</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.1248477024154722</v>
+        <v>0.1232062697309475</v>
       </c>
     </row>
     <row r="66">
@@ -20021,13 +20823,13 @@
         </is>
       </c>
       <c r="B66" s="28" t="n">
-        <v>0</v>
+        <v>-0.002126740210275313</v>
       </c>
       <c r="C66" s="28" t="n">
-        <v>0.07297573683573966</v>
+        <v>0.07069900685594488</v>
       </c>
       <c r="D66" s="28" t="n">
-        <v>0.1368786505476266</v>
+        <v>0.1344902043471298</v>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
@@ -20035,13 +20837,13 @@
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>0</v>
+        <v>0.007417864679201358</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>0.02422584232023706</v>
+        <v>0.03182341101950947</v>
       </c>
       <c r="I66" s="22" t="n">
-        <v>0.07816509080384493</v>
+        <v>0.08616277354926649</v>
       </c>
       <c r="P66" s="19" t="inlineStr">
         <is>
@@ -20056,13 +20858,13 @@
         </is>
       </c>
       <c r="G67" s="22" t="n">
-        <v>0</v>
+        <v>-0.01190032361798432</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>0.05450977998621331</v>
+        <v>0.04196077234604778</v>
       </c>
       <c r="I67" s="22" t="n">
-        <v>0.07689227589474101</v>
+        <v>0.06407690930988585</v>
       </c>
       <c r="K67" s="19" t="inlineStr">
         <is>
@@ -20102,13 +20904,13 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>0</v>
+        <v>0.001929961520374168</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>0.03298825606452294</v>
+        <v>0.03483115782928111</v>
       </c>
       <c r="I68" s="28" t="n">
-        <v>0.09113721172486418</v>
+        <v>0.09336069017850994</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
@@ -20136,13 +20938,13 @@
         </is>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>0</v>
+        <v>0.002913395255716766</v>
       </c>
       <c r="R68" s="22" t="n">
-        <v>0.07601875360150312</v>
+        <v>0.07915362153330796</v>
       </c>
       <c r="S68" s="22" t="n">
-        <v>0.2550274285984273</v>
+        <v>0.2586838195547003</v>
       </c>
     </row>
     <row r="69">
@@ -20172,13 +20974,13 @@
         </is>
       </c>
       <c r="L69" s="31" t="n">
-        <v>0</v>
+        <v>-0.01149099916922081</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>0.01708515145353395</v>
+        <v>0.005397826823154706</v>
       </c>
       <c r="N69" s="31" t="n">
-        <v>0.1345967938823085</v>
+        <v>0.1215591430664062</v>
       </c>
       <c r="P69" s="20" t="inlineStr">
         <is>
@@ -20186,13 +20988,13 @@
         </is>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>0</v>
+        <v>-0.000396913236870966</v>
       </c>
       <c r="R69" s="22" t="n">
-        <v>0.08249194877603117</v>
+        <v>0.08206229339275573</v>
       </c>
       <c r="S69" s="22" t="n">
-        <v>0.1533531923446558</v>
+        <v>0.1528954111958269</v>
       </c>
     </row>
     <row r="70">
@@ -20202,13 +21004,13 @@
         </is>
       </c>
       <c r="B70" s="22" t="n">
-        <v>0</v>
+        <v>-0.008037841979156357</v>
       </c>
       <c r="C70" s="22" t="n">
-        <v>0.03110709141882317</v>
+        <v>0.02281921555441113</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>0.07055145623710146</v>
+        <v>0.06194653280131202</v>
       </c>
       <c r="F70" s="19" t="inlineStr">
         <is>
@@ -20221,13 +21023,13 @@
         </is>
       </c>
       <c r="L70" s="22" t="n">
-        <v>0</v>
+        <v>-0.003811739309999562</v>
       </c>
       <c r="M70" s="22" t="n">
-        <v>0.02830824859976966</v>
+        <v>0.02438860562578515</v>
       </c>
       <c r="N70" s="22" t="n">
-        <v>0.1213195848521145</v>
+        <v>0.1170454069114613</v>
       </c>
       <c r="P70" s="26" t="inlineStr">
         <is>
@@ -20235,13 +21037,13 @@
         </is>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>0</v>
+        <v>0.0012582410094229</v>
       </c>
       <c r="R70" s="28" t="n">
-        <v>0.07925535118876714</v>
+        <v>0.08060795746303184</v>
       </c>
       <c r="S70" s="28" t="n">
-        <v>0.2041903104715416</v>
+        <v>0.2057896153752636</v>
       </c>
     </row>
     <row r="71">
@@ -20251,13 +21053,13 @@
         </is>
       </c>
       <c r="B71" s="22" t="n">
-        <v>0</v>
+        <v>0.001862544150731393</v>
       </c>
       <c r="C71" s="22" t="n">
-        <v>0.00773301342136401</v>
+        <v>0.009609960651011162</v>
       </c>
       <c r="D71" s="22" t="n">
-        <v>0.02438378504147232</v>
+        <v>0.02629174506840548</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -20285,13 +21087,13 @@
         </is>
       </c>
       <c r="L71" s="22" t="n">
-        <v>0</v>
+        <v>-0.0176755822803446</v>
       </c>
       <c r="M71" s="22" t="n">
-        <v>0.02755109939183864</v>
+        <v>0.009388535387279573</v>
       </c>
       <c r="N71" s="22" t="n">
-        <v>0.121034944773782</v>
+        <v>0.1012199993682914</v>
       </c>
     </row>
     <row r="72">
@@ -20301,13 +21103,13 @@
         </is>
       </c>
       <c r="B72" s="28" t="n">
-        <v>0</v>
+        <v>-0.003087648914212482</v>
       </c>
       <c r="C72" s="28" t="n">
-        <v>0.01942005242009359</v>
+        <v>0.01621458810271115</v>
       </c>
       <c r="D72" s="28" t="n">
-        <v>0.04746762063928689</v>
+        <v>0.04411913893485875</v>
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
@@ -20329,13 +21131,13 @@
         </is>
       </c>
       <c r="L72" s="31" t="n">
-        <v>0</v>
+        <v>-0.01961587599354675</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>0.02259256902701745</v>
+        <v>0.002533520001061218</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>0.09323365607463074</v>
+        <v>0.0717889202450992</v>
       </c>
       <c r="P72" s="19" t="inlineStr">
         <is>
@@ -20346,17 +21148,17 @@
     <row r="73">
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>Tempus AI</t>
+          <t>Twist</t>
         </is>
       </c>
       <c r="G73" s="22" t="n">
-        <v>0</v>
+        <v>0.03809320969700858</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>0.05090148760158097</v>
+        <v>0.03920723731864983</v>
       </c>
       <c r="I73" s="22" t="n">
-        <v>-0.1240446207383522</v>
+        <v>-0.1175577483961122</v>
       </c>
       <c r="K73" s="26" t="inlineStr">
         <is>
@@ -20364,13 +21166,13 @@
         </is>
       </c>
       <c r="L73" s="28" t="n">
-        <v>0</v>
+        <v>-0.01314854918827793</v>
       </c>
       <c r="M73" s="28" t="n">
-        <v>0.02388426711803993</v>
+        <v>0.01042712195932016</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.1175462448957089</v>
+        <v>0.1029033673978145</v>
       </c>
       <c r="P73" s="5" t="inlineStr">
         <is>
@@ -20405,13 +21207,13 @@
         </is>
       </c>
       <c r="G74" s="22" t="n">
-        <v>0</v>
+        <v>0.0294117097073654</v>
       </c>
       <c r="H74" s="22" t="n">
-        <v>0.07494149252711302</v>
+        <v>0.1065573596577225</v>
       </c>
       <c r="I74" s="22" t="n">
-        <v>-0.1428571174156512</v>
+        <v>-0.1176470797753461</v>
       </c>
       <c r="P74" s="20" t="inlineStr">
         <is>
@@ -20419,13 +21221,13 @@
         </is>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>0</v>
+        <v>0.006012898212634177</v>
       </c>
       <c r="R74" s="22" t="n">
-        <v>0.02573673064560378</v>
+        <v>0.03190438119993599</v>
       </c>
       <c r="S74" s="22" t="n">
-        <v>0.08874163952989411</v>
+        <v>0.09528813218824395</v>
       </c>
     </row>
     <row r="75">
@@ -20451,17 +21253,17 @@
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>Twist</t>
+          <t>Tempus AI</t>
         </is>
       </c>
       <c r="G75" s="22" t="n">
-        <v>0</v>
+        <v>-0.006729190505586846</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>0.001073147970948041</v>
+        <v>0.04382977128890531</v>
       </c>
       <c r="I75" s="22" t="n">
-        <v>-0.1499392893038488</v>
+        <v>-0.1299390913597974</v>
       </c>
       <c r="P75" s="20" t="inlineStr">
         <is>
@@ -20469,13 +21271,13 @@
         </is>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>0</v>
+        <v>0.02466287037962056</v>
       </c>
       <c r="R75" s="22" t="n">
-        <v>0.07093993287215472</v>
+        <v>0.0973523856209404</v>
       </c>
       <c r="S75" s="22" t="n">
-        <v>-0.04560849889383256</v>
+        <v>-0.02207046501063958</v>
       </c>
     </row>
     <row r="76">
@@ -20485,13 +21287,13 @@
         </is>
       </c>
       <c r="B76" s="22" t="n">
-        <v>0</v>
+        <v>0.03809320969700858</v>
       </c>
       <c r="C76" s="22" t="n">
-        <v>0.001073147970948041</v>
+        <v>0.03920723731864983</v>
       </c>
       <c r="D76" s="22" t="n">
-        <v>-0.1499392893038488</v>
+        <v>-0.1175577483961122</v>
       </c>
       <c r="F76" s="29" t="inlineStr">
         <is>
@@ -20499,13 +21301,13 @@
         </is>
       </c>
       <c r="G76" s="31" t="n">
-        <v>0</v>
+        <v>0.0294117977049948</v>
       </c>
       <c r="H76" s="31" t="n">
-        <v>0.0294116943401328</v>
+        <v>0.05968854284922065</v>
       </c>
       <c r="I76" s="31" t="n">
-        <v>-0.2247557444431232</v>
+        <v>-0.2019544172267251</v>
       </c>
       <c r="P76" s="26" t="inlineStr">
         <is>
@@ -20513,13 +21315,13 @@
         </is>
       </c>
       <c r="Q76" s="28" t="n">
-        <v>0</v>
+        <v>0.01533788429612737</v>
       </c>
       <c r="R76" s="28" t="n">
-        <v>0.04833833175887925</v>
+        <v>0.06462838341043819</v>
       </c>
       <c r="S76" s="28" t="n">
-        <v>0.02156657031803078</v>
+        <v>0.03660883358880218</v>
       </c>
     </row>
     <row r="77">
@@ -20529,13 +21331,13 @@
         </is>
       </c>
       <c r="B77" s="22" t="n">
-        <v>0.001898717253736804</v>
+        <v>0.003164568995649875</v>
       </c>
       <c r="C77" s="22" t="n">
-        <v>-0.04924923204872733</v>
+        <v>-0.04804800332669101</v>
       </c>
       <c r="D77" s="22" t="n">
-        <v>-0.2174987502764855</v>
+        <v>-0.216510096879736</v>
       </c>
       <c r="F77" s="26" t="inlineStr">
         <is>
@@ -20543,13 +21345,13 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>0.00168067058527952</v>
+        <v>0.01971817590603591</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>0.02961267355440243</v>
+        <v>0.04820369128934712</v>
       </c>
       <c r="I77" s="28" t="n">
-        <v>-0.1231911335768691</v>
+        <v>-0.1082914465482702</v>
       </c>
     </row>
     <row r="78">
@@ -20559,13 +21361,13 @@
         </is>
       </c>
       <c r="B78" s="28" t="n">
-        <v>0.0009493586268684018</v>
+        <v>0.02062888934632923</v>
       </c>
       <c r="C78" s="28" t="n">
-        <v>-0.02408804203888965</v>
+        <v>-0.004420383004020589</v>
       </c>
       <c r="D78" s="28" t="n">
-        <v>-0.1837190197901671</v>
+        <v>-0.1670339226379241</v>
       </c>
     </row>
   </sheetData>
@@ -22337,10 +23139,10 @@
         <v>-0.01021656799186726</v>
       </c>
       <c r="U15" s="22" t="n">
-        <v>0</v>
+        <v>0.0004239605735966527</v>
       </c>
       <c r="V15" s="22" t="n">
-        <v>0.03428110641681145</v>
+        <v>0.03480742203195401</v>
       </c>
     </row>
     <row r="16">
@@ -22407,10 +23209,10 @@
         <v>0.01893172614844548</v>
       </c>
       <c r="U16" s="22" t="n">
-        <v>-0.003080538355565036</v>
+        <v>0.001800718025942188</v>
       </c>
       <c r="V16" s="22" t="n">
-        <v>-0.003434493321900886</v>
+        <v>0.001610370758077525</v>
       </c>
     </row>
     <row r="17">
@@ -22477,10 +23279,10 @@
         <v>-0.01377505645905812</v>
       </c>
       <c r="U17" s="22" t="n">
-        <v>-0.002332011541228196</v>
+        <v>0.004657423318040044</v>
       </c>
       <c r="V17" s="22" t="n">
-        <v>-0.02501970099113868</v>
+        <v>-0.01728935086455179</v>
       </c>
     </row>
     <row r="18">
@@ -22547,10 +23349,10 @@
         <v>-0.03886286028860549</v>
       </c>
       <c r="U18" s="22" t="n">
-        <v>0</v>
+        <v>-0.03433912145115157</v>
       </c>
       <c r="V18" s="22" t="n">
-        <v>-0.120466775473631</v>
+        <v>-0.1521029365085169</v>
       </c>
     </row>
     <row r="19">
@@ -22617,10 +23419,10 @@
         <v>-0.0205403620409313</v>
       </c>
       <c r="U19" s="22" t="n">
-        <v>0</v>
+        <v>0.01199982353310909</v>
       </c>
       <c r="V19" s="22" t="n">
-        <v>-0.144327711425969</v>
+        <v>-0.1340826469635428</v>
       </c>
     </row>
     <row r="20">
@@ -22687,10 +23489,10 @@
         <v>0.0019500824884503</v>
       </c>
       <c r="U20" s="22" t="n">
-        <v>-0.008208955223880588</v>
+        <v>-0.01077246073624276</v>
       </c>
       <c r="V20" s="22" t="n">
-        <v>-0.04707002994280454</v>
+        <v>-0.04966339046778119</v>
       </c>
     </row>
     <row r="21">
@@ -22757,10 +23559,10 @@
         <v>-0.0219387483039406</v>
       </c>
       <c r="U21" s="22" t="n">
-        <v>0</v>
+        <v>-0.008141983501841532</v>
       </c>
       <c r="V21" s="22" t="n">
-        <v>-0.1181548063071474</v>
+        <v>-0.1242493851130877</v>
       </c>
     </row>
     <row r="22">
@@ -22827,10 +23629,10 @@
         <v>-0.01493811528464978</v>
       </c>
       <c r="U22" s="22" t="n">
-        <v>0</v>
+        <v>-0.004895597362709586</v>
       </c>
       <c r="V22" s="22" t="n">
-        <v>-0.1053232508927331</v>
+        <v>-0.1101848762337985</v>
       </c>
     </row>
     <row r="23">
@@ -22897,10 +23699,10 @@
         <v>0.01351822076694492</v>
       </c>
       <c r="U23" s="22" t="n">
-        <v>-0.01847573328305802</v>
+        <v>-0.04578519042151813</v>
       </c>
       <c r="V23" s="22" t="n">
-        <v>-0.1133613198719495</v>
+        <v>-0.1380411464670162</v>
       </c>
     </row>
     <row r="24">
@@ -22967,10 +23769,10 @@
         <v>-0.02373605263493837</v>
       </c>
       <c r="U24" s="22" t="n">
-        <v>0</v>
+        <v>-0.001364955843363505</v>
       </c>
       <c r="V24" s="22" t="n">
-        <v>-0.09222444875560777</v>
+        <v>-0.09322491154306671</v>
       </c>
     </row>
     <row r="25">
@@ -23037,10 +23839,10 @@
         <v>-0.001833740854555566</v>
       </c>
       <c r="U25" s="22" t="n">
-        <v>0</v>
+        <v>-0.0002118985753747915</v>
       </c>
       <c r="V25" s="22" t="n">
-        <v>0.04622498590955321</v>
+        <v>0.04582324406866789</v>
       </c>
     </row>
     <row r="26">
@@ -23107,10 +23909,10 @@
         <v>0.003613799429639501</v>
       </c>
       <c r="U26" s="22" t="n">
-        <v>0</v>
+        <v>-0.01248495741457127</v>
       </c>
       <c r="V26" s="22" t="n">
-        <v>0.02237183598229908</v>
+        <v>0.009623593550883233</v>
       </c>
     </row>
     <row r="27">
@@ -23177,10 +23979,10 @@
         <v>0.00582778469961102</v>
       </c>
       <c r="U27" s="22" t="n">
-        <v>0</v>
+        <v>0.03136605124068555</v>
       </c>
       <c r="V27" s="22" t="n">
-        <v>-0.02145404762432883</v>
+        <v>0.009489397443678086</v>
       </c>
     </row>
     <row r="28">
@@ -23247,10 +24049,10 @@
         <v>-0.02208176775999497</v>
       </c>
       <c r="U28" s="22" t="n">
-        <v>0</v>
+        <v>0.002304390359192535</v>
       </c>
       <c r="V28" s="22" t="n">
-        <v>-0.05984565386903754</v>
+        <v>-0.05848400898118474</v>
       </c>
     </row>
     <row r="29">
@@ -23317,10 +24119,10 @@
         <v>0.003011441046590513</v>
       </c>
       <c r="U29" s="22" t="n">
-        <v>0</v>
+        <v>-0.002126740210275313</v>
       </c>
       <c r="V29" s="22" t="n">
-        <v>0.1368786505476266</v>
+        <v>0.1344902043471298</v>
       </c>
     </row>
     <row r="30">
@@ -23387,10 +24189,10 @@
         <v>0.01901543838086117</v>
       </c>
       <c r="U30" s="22" t="n">
-        <v>0</v>
+        <v>-0.001459248821862547</v>
       </c>
       <c r="V30" s="22" t="n">
-        <v>0.1248477024154722</v>
+        <v>0.1232062697309475</v>
       </c>
     </row>
     <row r="31">
@@ -23457,10 +24259,10 @@
         <v>0.0005667618886181872</v>
       </c>
       <c r="U31" s="22" t="n">
-        <v>0</v>
+        <v>0.001929961520374168</v>
       </c>
       <c r="V31" s="22" t="n">
-        <v>0.09113721172486418</v>
+        <v>0.09336069017850994</v>
       </c>
     </row>
     <row r="32">
@@ -23527,10 +24329,10 @@
         <v>0.01096553184388771</v>
       </c>
       <c r="U32" s="22" t="n">
-        <v>0</v>
+        <v>0.0012582410094229</v>
       </c>
       <c r="V32" s="22" t="n">
-        <v>0.2041903104715416</v>
+        <v>0.2057896153752636</v>
       </c>
     </row>
     <row r="33">
@@ -23597,10 +24399,10 @@
         <v>-0.01345992656600267</v>
       </c>
       <c r="U33" s="22" t="n">
-        <v>0</v>
+        <v>-0.01314854918827793</v>
       </c>
       <c r="V33" s="22" t="n">
-        <v>0.1175462448957089</v>
+        <v>0.1029033673978145</v>
       </c>
     </row>
     <row r="34">
@@ -23667,10 +24469,10 @@
         <v>-0.002187304161930081</v>
       </c>
       <c r="U34" s="22" t="n">
-        <v>0</v>
+        <v>-0.003087648914212482</v>
       </c>
       <c r="V34" s="22" t="n">
-        <v>0.04746762063928689</v>
+        <v>0.04411913893485875</v>
       </c>
     </row>
     <row r="35">
@@ -23737,10 +24539,10 @@
         <v>0.02505970617698629</v>
       </c>
       <c r="U35" s="22" t="n">
-        <v>0.00168067058527952</v>
+        <v>0.01971817590603591</v>
       </c>
       <c r="V35" s="22" t="n">
-        <v>-0.1231911335768691</v>
+        <v>-0.1082914465482702</v>
       </c>
     </row>
     <row r="36">
@@ -23807,10 +24609,10 @@
         <v>0.01887844489286772</v>
       </c>
       <c r="U36" s="22" t="n">
-        <v>0</v>
+        <v>0.01533788429612737</v>
       </c>
       <c r="V36" s="22" t="n">
-        <v>0.02156657031803078</v>
+        <v>0.03660883358880218</v>
       </c>
     </row>
     <row r="37">
@@ -23877,10 +24679,10 @@
         <v>-0.003040440832455027</v>
       </c>
       <c r="U37" s="22" t="n">
-        <v>0.0009493586268684018</v>
+        <v>0.02062888934632923</v>
       </c>
       <c r="V37" s="22" t="n">
-        <v>-0.1837190197901671</v>
+        <v>-0.1670339226379241</v>
       </c>
     </row>
   </sheetData>
@@ -24403,7 +25205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -24828,14 +25630,471 @@
       </c>
       <c r="E26" s="7" t="inlineStr"/>
     </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>🌐 글로벌 코멘트 (미국장 마감)</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>① 섹터 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+    </row>
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>미국 SOX +2.8%·SMH +2.7%로 NASDAQ(+0.8%)를 웃돌았다. 아시아는 닛케이225 0.0%, TOPIX 전기·정밀 -2.0%로 상대 약세다.</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>10.22 급락 뒤 EDA·IP(+4.5%)와 GPU(+1.9%)로 자금이 들어오고 있다. 장비(-0.7%)는 이탈했고, 20D 누적은 OSAT(-16.0%)·장비(-12.3%)가 가장 부진하다.</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>국가별 1D 평균은 US +2.2%·IL +1.7%로 강하고, JP -1.6%·CA -5.1%는 약하다. TW 평균은 0.0%다.</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>한국 시사점: 미 반도체 반등은 국내 반도체 수급에 우호적이지만, 일본 장비 약세와 DDR5 현물 $61.33(+0.4%) 횡보로 메모리 가격 모멘텀은 제한적이다.</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="31" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>체크포인트: Nvidia 5D -0.5%와 Micron 20D -17.6%의 반등 지속 여부, DDR5 현물 추이를 확인해야 한다. 10.23 Lam 가이던스 하향 여파가 장비 그룹 반등을 제한하는지도 본다.</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>② 종목 코멘트</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>등락</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1">
+      <c r="A41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Lumentum (US)</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>+8.2%</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 10.26 AI 랙 광학 기술 시연 발표가 부각된 것으로 보인다. 양산·매출 기여 수치는 확인되지 않았다.</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026 루멘텀 시연 발표)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17.5" customHeight="1">
+      <c r="A42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Arm (US)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>+6.2%</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 20D -33.0% 낙폭 뒤 단기 반등이다.</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="17.5" customHeight="1">
+      <c r="A43" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Synopsys (US)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>+5.6%</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. EDA·IP 그룹 1D +4.5%와 같은 방향이다.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Texas Instruments (US)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>+4.7%</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 아날로그 동료 Analog Devices도 +4.3%로 동조했다.</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Intel (US)</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 10.26 Crescent Island GPU 공개 등 AI 제품 뉴스가 반영된 듯하다. 20D는 -27.0%로 여전히 부진하다.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026 인텔 Crescent Island)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="31" customHeight="1">
+      <c r="A46" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Micron (US)</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. DDR5 현물 $61.33로 횡보 중이며 20D는 -17.6%다.</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr"/>
+    </row>
+    <row r="47" ht="31" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Lam Research (US)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 9월 분기 사상 최대 실적 발표가 반영된 듯하다. 5D -12.7%는 10.23 신중 가이던스·중국 매출 감소 낙폭의 영향이다.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026 램리서치 실적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="31" customHeight="1">
+      <c r="A48" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Nvidia (US)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>+2.4%</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 젠슨 황의 Vera Rubin GW당 매출 400억 달러 발언이 반영된 듯하나, 5D -0.5%로 방향성은 약하다.</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026 젠슨 황 발언)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Amkor (US)</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>-6.3%</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>10.26 직접 원인은 미확인이다. [추정] 10.23 엔비디아 13억 달러 계약 뉴스 뒤 차익실현일 수 있으며, 5D는 -12.1%다.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1023 앰코 엔비디아 계약)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>Nebius (US)</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>-3.4%</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 10.26 씨티 35억 달러 담보부 조달 뉴스 이후 자금조달·희석 우려가 재부각된 듯하다. 5D -10.0%, 20D -35.1%다.</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026 네비우스·씨티 35억 달러)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17.5" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Advantest (JP)</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>-3.9%</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. 5D -9.8%로 단기 낙폭이 크다.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="31" customHeight="1">
+      <c r="A52" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Tokyo Electron (JP)</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>-3.7%</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반. SCREEN -4.3%, Kokusai -4.3%와 동조했고 5D는 -12.0%다.</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr"/>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Rorze (JP)</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터 동반 하락은 아니다. 5D -21.2%로 장비 그룹 내 최대 낙폭이다.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="31" customHeight="1">
+      <c r="A54" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Celestica (CA)</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>-5.1%</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 10월 AI 하드웨어 차익실현 흐름이 이어진 것으로 보이나 10.26 직접 뉴스는 확인되지 않았다. 5D -17.9%, 20D -30.7%다.</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="14">
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25012,22 +26271,22 @@
         </is>
       </c>
       <c r="L5" s="21" t="n">
-        <v>4.98799991607666</v>
+        <v>4.986000061035156</v>
       </c>
       <c r="M5" s="21" t="n">
-        <v>0</v>
+        <v>-0.001999855041503906</v>
       </c>
       <c r="N5" s="21" t="n">
-        <v>-0.1480002403259277</v>
+        <v>-0.1500000953674316</v>
       </c>
       <c r="O5" s="21" t="n">
-        <v>-0.1960000991821289</v>
+        <v>-0.1979999542236328</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>0.3090000152587891</v>
+        <v>0.3070001602172852</v>
       </c>
       <c r="Q5" s="21" t="n">
-        <v>0.8249998092651367</v>
+        <v>0.8229999542236328</v>
       </c>
     </row>
     <row r="6">
@@ -25070,22 +26329,22 @@
         </is>
       </c>
       <c r="L6" s="21" t="n">
-        <v>1323.0400390625</v>
+        <v>1325.170043945312</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>-2.949951171875</v>
+        <v>-0.8199462890625</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>-10.3900146484375</v>
+        <v>-8.260009765625</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>-44.3199462890625</v>
+        <v>-42.18994140625</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>-151</v>
+        <v>-148.8699951171875</v>
       </c>
       <c r="Q6" s="21" t="n">
-        <v>-114.8699951171875</v>
+        <v>-112.739990234375</v>
       </c>
     </row>
     <row r="7">
@@ -25128,22 +26387,22 @@
         </is>
       </c>
       <c r="L7" s="21" t="n">
-        <v>156.9349975585938</v>
+        <v>157.4420013427734</v>
       </c>
       <c r="M7" s="21" t="n">
-        <v>0.4409942626953125</v>
+        <v>0.947998046875</v>
       </c>
       <c r="N7" s="21" t="n">
-        <v>-0.871002197265625</v>
+        <v>-0.3639984130859375</v>
       </c>
       <c r="O7" s="21" t="n">
-        <v>-1.876007080078125</v>
+        <v>-1.369003295898438</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>-6.897003173828125</v>
+        <v>-6.389999389648438</v>
       </c>
       <c r="Q7" s="21" t="n">
-        <v>0.522003173828125</v>
+        <v>1.029006958007812</v>
       </c>
     </row>
     <row r="8">
@@ -25186,22 +26445,22 @@
         </is>
       </c>
       <c r="L8" s="21" t="n">
-        <v>61.3</v>
+        <v>61.333</v>
       </c>
       <c r="M8" s="21" t="n">
-        <v>0.03299999999999415</v>
+        <v>0.0659999999999954</v>
       </c>
       <c r="N8" s="21" t="n">
-        <v>0.6669999999999945</v>
+        <v>0.6999999999999957</v>
       </c>
       <c r="O8" s="21" t="n">
-        <v>3.632999999999996</v>
+        <v>3.665999999999997</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>10.467</v>
+        <v>10.5</v>
       </c>
       <c r="Q8" s="21" t="n">
-        <v>32.325</v>
+        <v>32.358</v>
       </c>
     </row>
     <row r="9">
@@ -25276,22 +26535,22 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>25955.33984375</v>
+        <v>26169.380859375</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>0</v>
+        <v>0.008246511774205878</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-0.01799223446523568</v>
+        <v>-0.009894095864391605</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.0411316394145832</v>
+        <v>-0.03322432018910204</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>0.03921871309907554</v>
+        <v>0.04778864245262215</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0.1167434278223707</v>
+        <v>0.1259526656486749</v>
       </c>
     </row>
     <row r="12">
@@ -25306,22 +26565,22 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>7623.68017578125</v>
+        <v>7676.77001953125</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>0</v>
+        <v>0.006963807836358971</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.008718262747200667</v>
+        <v>-0.001815167217280034</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.01546217726463983</v>
+        <v>-0.008606045059483591</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.02856189518459984</v>
+        <v>0.0357246025704665</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0.1136776241006865</v>
+        <v>0.1214330610665766</v>
       </c>
     </row>
     <row r="13">
@@ -25336,22 +26595,22 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>10779.4599609375</v>
+        <v>11083.4697265625</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>0</v>
+        <v>0.02820268981253871</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.04744289144948377</v>
+        <v>-0.0205782187883049</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.1491420169792855</v>
+        <v>-0.1251455332096301</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>-0.08794572177576376</v>
+        <v>-0.06222333787480683</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0.5218498233520035</v>
+        <v>0.5647700818612666</v>
       </c>
     </row>
     <row r="14">
@@ -25366,22 +26625,22 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>527.2000122070312</v>
+        <v>541.6199951171875</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0</v>
+        <v>0.02735201550885691</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.038763098336974</v>
+        <v>-0.01247133169500136</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.1308361673552274</v>
+        <v>-0.1070627847249901</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.06056770449670279</v>
+        <v>-0.03487233778057552</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>0.4639158222280975</v>
+        <v>0.5039568705013415</v>
       </c>
     </row>
     <row r="15">
@@ -25426,22 +26685,22 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>62189.6484375</v>
+        <v>62693.16015625</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>-0.008031366061227452</v>
+        <v>0</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.04200846337027475</v>
+        <v>-0.03425218917874018</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.06290371150297758</v>
+        <v>-0.05531661341334004</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>-0.03747805229529977</v>
+        <v>-0.02968509812366693</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>0.2354050510335801</v>
+        <v>0.2454073735458788</v>
       </c>
     </row>
     <row r="17">
@@ -25486,22 +26745,22 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>3.779999971389771</v>
+        <v>3.79800009727478</v>
       </c>
       <c r="D18" s="22" t="n">
-        <v>-0.004739369516584713</v>
+        <v>0</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>-0.0615689955451002</v>
+        <v>-0.05710024518995827</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>-0.1084905246603547</v>
+        <v>-0.1042452117224574</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>-0.1677674760510575</v>
+        <v>-0.1638044362864903</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>-0.2987012866376159</v>
+        <v>-0.2953617455743716</v>
       </c>
     </row>
     <row r="20">
@@ -25986,16 +27245,16 @@
         </is>
       </c>
       <c r="J31" s="22" t="n">
-        <v>0</v>
+        <v>0.008246511774205878</v>
       </c>
       <c r="K31" s="22" t="n">
-        <v>0</v>
+        <v>0.006963807836358971</v>
       </c>
       <c r="L31" s="22" t="n">
-        <v>0</v>
+        <v>0.02820268981253871</v>
       </c>
       <c r="M31" s="22" t="n">
-        <v>0</v>
+        <v>0.02735201550885691</v>
       </c>
     </row>
     <row r="33">
@@ -26396,13 +27655,13 @@
         <v>0</v>
       </c>
       <c r="C44" s="22" t="n">
-        <v>-0.008031366061227452</v>
+        <v>0</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>-0.0195729537366548</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>-0.004739369516584713</v>
+        <v>0</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -26410,16 +27669,16 @@
         </is>
       </c>
       <c r="J44" s="21" t="n">
-        <v>4.98799991607666</v>
+        <v>4.986000061035156</v>
       </c>
       <c r="K44" s="23" t="n">
-        <v>1323.0400390625</v>
+        <v>1325.170043945312</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>156.9349975585938</v>
+        <v>157.4420013427734</v>
       </c>
       <c r="M44" s="21" t="n">
-        <v>61.3</v>
+        <v>61.333</v>
       </c>
     </row>
     <row r="46">
@@ -30958,341 +32217,341 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>0</v>
+        <v>0.08189956501240725</v>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="F5" s="22" t="n">
-        <v>0</v>
+        <v>-0.01019249206644313</v>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>Socionext (JP)</t>
+          <t>Lumentum (US)</t>
         </is>
       </c>
       <c r="J5" s="22" t="n">
-        <v>0.03788094559954436</v>
+        <v>0.08189956501240725</v>
       </c>
       <c r="M5" s="20" t="inlineStr">
         <is>
-          <t>Ibiden (JP)</t>
+          <t>SUMCO (JP)</t>
         </is>
       </c>
       <c r="N5" s="22" t="n">
-        <v>-0.03101503759398494</v>
+        <v>-0.03514376996805113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>Adobe Inc.</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>0</v>
+        <v>0.06486661705364205</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0</v>
+        <v>-0.01090404454114391</v>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>Taiyo Yuden (JP)</t>
+          <t>TTM Tech (US)</t>
         </is>
       </c>
       <c r="J6" s="22" t="n">
-        <v>0.02486848397895747</v>
+        <v>0.06728247844941304</v>
       </c>
       <c r="M6" s="20" t="inlineStr">
         <is>
-          <t>Resonac (JP)</t>
+          <t>Sumitomo Electric (JP)</t>
         </is>
       </c>
       <c r="N6" s="22" t="n">
-        <v>-0.03432137285491421</v>
+        <v>-0.03519781718963166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Coherent Corp.</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>0</v>
+        <v>0.05834013620122858</v>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>0</v>
+        <v>-0.01098555546984104</v>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>Nitto Denko (JP)</t>
+          <t>Arm (US)</t>
         </is>
       </c>
       <c r="J7" s="22" t="n">
-        <v>0.01121076233183849</v>
+        <v>0.06190274406463003</v>
       </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
-          <t>SUMCO (JP)</t>
+          <t>Renesas (JP)</t>
         </is>
       </c>
       <c r="N7" s="22" t="n">
-        <v>-0.03514376996805113</v>
+        <v>-0.0356833535423523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>0</v>
+        <v>0.05623743688110272</v>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>0</v>
+        <v>-0.01138637802593911</v>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>Fujitsu (JP)</t>
+          <t>Coherent (US)</t>
         </is>
       </c>
       <c r="J8" s="22" t="n">
-        <v>0.006254188072369882</v>
+        <v>0.05834013620122858</v>
       </c>
       <c r="M8" s="20" t="inlineStr">
         <is>
-          <t>Sumitomo Electric (JP)</t>
+          <t>Tokyo Electron (JP)</t>
         </is>
       </c>
       <c r="N8" s="22" t="n">
-        <v>-0.03519781718963166</v>
+        <v>-0.03679424825544508</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>0</v>
+        <v>0.05313804432341396</v>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>0</v>
+        <v>-0.01701168928355612</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>Nidec (JP)</t>
+          <t>Synopsys (US)</t>
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.00175953079178881</v>
+        <v>0.05623743688110272</v>
       </c>
       <c r="M9" s="20" t="inlineStr">
         <is>
-          <t>Renesas (JP)</t>
+          <t>Advantest (JP)</t>
         </is>
       </c>
       <c r="N9" s="22" t="n">
-        <v>-0.0356833535423523</v>
+        <v>-0.0392702535559678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0</v>
+        <v>0.04892894033702166</v>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Gen Digital</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>0</v>
+        <v>-0.01889064828007059</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>Hoya (JP)</t>
+          <t>Ciena (US)</t>
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.0003831417624520217</v>
+        <v>0.04892894033702166</v>
       </c>
       <c r="M10" s="20" t="inlineStr">
         <is>
-          <t>Tokyo Electron (JP)</t>
+          <t>Kokusai (JP)</t>
         </is>
       </c>
       <c r="N10" s="22" t="n">
-        <v>-0.03679424825544508</v>
+        <v>-0.04294928173556145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0</v>
+        <v>0.04717409308584819</v>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Adobe Inc.</t>
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>0</v>
+        <v>-0.01971045433502983</v>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>CoreWeave (US)</t>
+          <t>Texas Instruments (US)</t>
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0</v>
+        <v>0.04717409308584819</v>
       </c>
       <c r="M11" s="20" t="inlineStr">
         <is>
-          <t>Advantest (JP)</t>
+          <t>SCREEN (JP)</t>
         </is>
       </c>
       <c r="N11" s="22" t="n">
-        <v>-0.0392702535559678</v>
+        <v>-0.04342218400687881</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>NXP Semiconductors</t>
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>0</v>
+        <v>0.0464413576840883</v>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0</v>
+        <v>-0.02232694618311593</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>Oracle (US)</t>
+          <t>Analog Devices (US)</t>
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0</v>
+        <v>0.04311244799089042</v>
       </c>
       <c r="M12" s="20" t="inlineStr">
         <is>
-          <t>Kokusai (JP)</t>
+          <t>Celestica (CA)</t>
         </is>
       </c>
       <c r="N12" s="22" t="n">
-        <v>-0.04294928173556145</v>
+        <v>-0.0513826982322082</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>0</v>
+        <v>0.04311244799089042</v>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>GoDaddy</t>
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0</v>
+        <v>-0.0263321322510448</v>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>Apple (US)</t>
+          <t>Entegris (US)</t>
         </is>
       </c>
       <c r="J13" s="22" t="n">
-        <v>0</v>
+        <v>0.04237285732386131</v>
       </c>
       <c r="M13" s="20" t="inlineStr">
         <is>
-          <t>SCREEN (JP)</t>
+          <t>Rorze (JP)</t>
         </is>
       </c>
       <c r="N13" s="22" t="n">
-        <v>-0.04342218400687881</v>
+        <v>-0.05933825540060156</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>0.04036341045520087</v>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Fair Isaac</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0</v>
+        <v>-0.1315327796243146</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>Microsoft (US)</t>
+          <t>Intel (US)</t>
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>0</v>
+        <v>0.04036341045520087</v>
       </c>
       <c r="M14" s="20" t="inlineStr">
         <is>
-          <t>Rorze (JP)</t>
+          <t>Amkor (US)</t>
         </is>
       </c>
       <c r="N14" s="22" t="n">
-        <v>-0.05933825540060156</v>
+        <v>-0.0633587254989415</v>
       </c>
     </row>
     <row r="15">
@@ -31302,7 +32561,7 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>0</v>
+        <v>0.0540502049024844</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
@@ -31310,7 +32569,7 @@
         </is>
       </c>
       <c r="F15" s="28" t="n">
-        <v>0</v>
+        <v>-0.02792731200604991</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -31318,7 +32577,7 @@
         </is>
       </c>
       <c r="J15" s="28" t="n">
-        <v>0.008235705253695103</v>
+        <v>0.05476141098016041</v>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
@@ -31326,7 +32585,7 @@
         </is>
       </c>
       <c r="N15" s="28" t="n">
-        <v>-0.03931355741033889</v>
+        <v>-0.04425405873856395</v>
       </c>
     </row>
     <row r="17">
@@ -31356,14 +32615,14 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>CA (1종목)</t>
+          <t>US (49종목)</t>
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>0</v>
+        <v>0.02225820468857467</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>0</v>
+        <v>0.0238133043279114</v>
       </c>
     </row>
     <row r="20">
@@ -31373,10 +32632,10 @@
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>0</v>
+        <v>0.01686993876923104</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>0</v>
+        <v>0.01686993876923104</v>
       </c>
     </row>
     <row r="21">
@@ -31386,10 +32645,10 @@
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0</v>
+        <v>0.01215165733082757</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0</v>
+        <v>0.01215165733082757</v>
       </c>
     </row>
     <row r="22">
@@ -31399,7 +32658,7 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>0</v>
+        <v>0.000359026143101323</v>
       </c>
       <c r="C22" s="22" t="n">
         <v>0</v>
@@ -31408,27 +32667,27 @@
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>US (49종목)</t>
+          <t>JP (32종목)</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>0</v>
+        <v>-0.01616463300143465</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0</v>
+        <v>-0.01537876463670296</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>JP (32종목)</t>
+          <t>CA (1종목)</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>-0.01616463300143465</v>
+        <v>-0.0513826982322082</v>
       </c>
       <c r="C24" s="22" t="n">
-        <v>-0.01537876463670296</v>
+        <v>-0.0513826982322082</v>
       </c>
     </row>
     <row r="26">
@@ -31542,13 +32801,13 @@
         </is>
       </c>
       <c r="B28" s="31" t="n">
-        <v>0</v>
+        <v>0.01542385401553625</v>
       </c>
       <c r="C28" s="31" t="n">
-        <v>-0.01688785694216532</v>
+        <v>-0.001724478766740312</v>
       </c>
       <c r="D28" s="31" t="n">
-        <v>0.05323295133659633</v>
+        <v>0.06947786262236444</v>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
@@ -31600,13 +32859,13 @@
         </is>
       </c>
       <c r="B29" s="22" t="n">
-        <v>0</v>
+        <v>-0.01098555546984104</v>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.01396748268158166</v>
+        <v>0.002828486655968021</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>0.02348789105615334</v>
+        <v>0.01224430805624532</v>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
@@ -31642,13 +32901,13 @@
         </is>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>0</v>
+        <v>0.04717409308584819</v>
       </c>
       <c r="R29" s="22" t="n">
-        <v>0.03092525342630692</v>
+        <v>0.07955821729599122</v>
       </c>
       <c r="S29" s="22" t="n">
-        <v>0.04892965845072439</v>
+        <v>0.09841196379898576</v>
       </c>
     </row>
     <row r="30">
@@ -31658,27 +32917,27 @@
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>0</v>
+        <v>0.004395146523752613</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>-0.05505815025694305</v>
+        <v>-0.05090499237089652</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>-0.02737467975722141</v>
+        <v>-0.02309984896204265</v>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>Alchip (TW)</t>
+          <t>Nvidia (US)</t>
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>0</v>
+        <v>0.02389075239729554</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>-0.05921938088829071</v>
+        <v>-0.005020942264857275</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>-0.05921938088829071</v>
+        <v>-0.05623277577560015</v>
       </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
@@ -31700,13 +32959,13 @@
         </is>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>0</v>
+        <v>0.04311244799089042</v>
       </c>
       <c r="R30" s="22" t="n">
-        <v>-0.008317481243897529</v>
+        <v>0.03443637976945002</v>
       </c>
       <c r="S30" s="22" t="n">
-        <v>0.001793201874598749</v>
+        <v>0.04498295918804485</v>
       </c>
     </row>
     <row r="31">
@@ -31716,27 +32975,27 @@
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>0</v>
+        <v>-0.01064927314295805</v>
       </c>
       <c r="C31" s="22" t="n">
-        <v>-0.06964379606830584</v>
+        <v>-0.07955141340422001</v>
       </c>
       <c r="D31" s="22" t="n">
-        <v>-0.08813649585449868</v>
+        <v>-0.09784717937923892</v>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>Nvidia (US)</t>
+          <t>Alchip (TW)</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>-0.02823708935202329</v>
+        <v>-0.05921938088829071</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>-0.07825398167265185</v>
+        <v>-0.05921938088829071</v>
       </c>
       <c r="K31" s="20" t="inlineStr">
         <is>
@@ -31774,13 +33033,13 @@
         </is>
       </c>
       <c r="B32" s="22" t="n">
-        <v>0</v>
+        <v>-0.01876691925279184</v>
       </c>
       <c r="C32" s="22" t="n">
-        <v>-0.08905081524553404</v>
+        <v>-0.1061465250392176</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>-0.1275861846098929</v>
+        <v>-0.143958704238339</v>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
@@ -31802,27 +33061,27 @@
         </is>
       </c>
       <c r="L32" s="22" t="n">
-        <v>0</v>
+        <v>0.0297989000943748</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>-0.03022437383489229</v>
+        <v>-0.001326126836838415</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>-0.1994326006880153</v>
+        <v>-0.1755765727371039</v>
       </c>
       <c r="P32" s="20" t="inlineStr">
         <is>
-          <t>Vanguard(VIS) (TW)</t>
+          <t>TSMC(ADR) (TW)</t>
         </is>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>0</v>
+        <v>0.0140020195809516</v>
       </c>
       <c r="R32" s="22" t="n">
-        <v>-0.01529051987767582</v>
+        <v>0.009875764800411746</v>
       </c>
       <c r="S32" s="22" t="n">
-        <v>-0.06936416184971095</v>
+        <v>-0.06112832938675328</v>
       </c>
     </row>
     <row r="33">
@@ -31832,27 +33091,27 @@
         </is>
       </c>
       <c r="B33" s="22" t="n">
-        <v>0</v>
+        <v>-0.0007926926174119941</v>
       </c>
       <c r="C33" s="22" t="n">
-        <v>-0.02646803590331115</v>
+        <v>-0.02723974750406521</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>-0.1544235506527888</v>
+        <v>-0.1550938328616438</v>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>GUC (TW)</t>
+          <t>Qualcomm (US)</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>0</v>
+        <v>0.02097664922168985</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>-0.03128991060025543</v>
+        <v>0.03497958489551345</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>-0.09432835820895524</v>
+        <v>-0.09416451186075103</v>
       </c>
       <c r="K33" s="20" t="inlineStr">
         <is>
@@ -31860,27 +33119,27 @@
         </is>
       </c>
       <c r="L33" s="22" t="n">
-        <v>0</v>
+        <v>0.03625568413957114</v>
       </c>
       <c r="M33" s="22" t="n">
-        <v>-0.02424683636049818</v>
+        <v>0.01112976213860284</v>
       </c>
       <c r="N33" s="22" t="n">
-        <v>-0.2602884009623481</v>
+        <v>-0.2334696508732619</v>
       </c>
       <c r="P33" s="20" t="inlineStr">
         <is>
-          <t>TSMC(ADR) (TW)</t>
+          <t>GlobalFoundries (US)</t>
         </is>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>0</v>
+        <v>0.01374184768503994</v>
       </c>
       <c r="R33" s="22" t="n">
-        <v>-0.004069276688664858</v>
+        <v>-0.02407288214397396</v>
       </c>
       <c r="S33" s="22" t="n">
-        <v>-0.07409289874861724</v>
+        <v>-0.06152243411890634</v>
       </c>
     </row>
     <row r="34">
@@ -31900,45 +33159,45 @@
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>Qualcomm (US)</t>
+          <t>GUC (TW)</t>
         </is>
       </c>
       <c r="G34" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>0.01371523597968505</v>
+        <v>-0.03128991060025543</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>-0.1127755087936784</v>
+        <v>-0.09432835820895524</v>
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>Kioxia (JP)</t>
+          <t>Seagate (US)</t>
         </is>
       </c>
       <c r="L34" s="22" t="n">
-        <v>-0.01607212857702867</v>
+        <v>0.02176090334627045</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>-0.07720588235294112</v>
+        <v>-0.02512064836680317</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>-0.3100604727872457</v>
+        <v>-0.299649935679654</v>
       </c>
       <c r="P34" s="20" t="inlineStr">
         <is>
-          <t>GlobalFoundries (US)</t>
+          <t>Vanguard(VIS) (TW)</t>
         </is>
       </c>
       <c r="Q34" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R34" s="22" t="n">
-        <v>-0.03730212964510327</v>
+        <v>-0.01529051987767582</v>
       </c>
       <c r="S34" s="22" t="n">
-        <v>-0.07424403162976678</v>
+        <v>-0.06936416184971095</v>
       </c>
     </row>
     <row r="35">
@@ -31948,13 +33207,13 @@
         </is>
       </c>
       <c r="B35" s="22" t="n">
-        <v>0</v>
+        <v>-0.03445887004797088</v>
       </c>
       <c r="C35" s="22" t="n">
-        <v>-0.0675516895496211</v>
+        <v>-0.09968280470588065</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>-0.3277146841614128</v>
+        <v>-0.3508808764950537</v>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
@@ -31962,27 +33221,27 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>0</v>
+        <v>0.02328407399431343</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-0.03858454766553154</v>
+        <v>-0.01619887913409934</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>-0.1175728722897065</v>
+        <v>-0.09702637375351053</v>
       </c>
       <c r="K35" s="20" t="inlineStr">
         <is>
-          <t>Seagate (US)</t>
+          <t>Kioxia (JP)</t>
         </is>
       </c>
       <c r="L35" s="22" t="n">
-        <v>0</v>
+        <v>-0.01607212857702867</v>
       </c>
       <c r="M35" s="22" t="n">
-        <v>-0.04588309413634484</v>
+        <v>-0.07720588235294112</v>
       </c>
       <c r="N35" s="22" t="n">
-        <v>-0.3145656072504859</v>
+        <v>-0.3100604727872457</v>
       </c>
       <c r="P35" s="20" t="inlineStr">
         <is>
@@ -32006,13 +33265,13 @@
         </is>
       </c>
       <c r="B36" s="31" t="n">
-        <v>0</v>
+        <v>0.01760851858781298</v>
       </c>
       <c r="C36" s="31" t="n">
-        <v>-0.1126472258156647</v>
+        <v>-0.09702225799749231</v>
       </c>
       <c r="D36" s="31" t="n">
-        <v>-0.3748847478681269</v>
+        <v>-0.3638773943314374</v>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
@@ -32020,13 +33279,13 @@
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>0</v>
+        <v>0.02306246728435024</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>-0.03618879734945391</v>
+        <v>-0.01396093302003554</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>-0.1290211645627574</v>
+        <v>-0.1089342436651246</v>
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
@@ -32034,13 +33293,13 @@
         </is>
       </c>
       <c r="L36" s="22" t="n">
-        <v>0</v>
+        <v>0.009552234868258846</v>
       </c>
       <c r="M36" s="22" t="n">
-        <v>-0.1374056589427536</v>
+        <v>-0.1291659552009438</v>
       </c>
       <c r="N36" s="22" t="n">
-        <v>-0.3384523302646968</v>
+        <v>-0.3321330715468358</v>
       </c>
       <c r="P36" s="20" t="inlineStr">
         <is>
@@ -32064,13 +33323,13 @@
         </is>
       </c>
       <c r="B37" s="28" t="n">
-        <v>-0.0003378027232096508</v>
+        <v>-0.004585112879195423</v>
       </c>
       <c r="C37" s="28" t="n">
-        <v>-0.06038488067880571</v>
+        <v>-0.06439639690464806</v>
       </c>
       <c r="D37" s="28" t="n">
-        <v>-0.1498155686764877</v>
+        <v>-0.1531084759073714</v>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
@@ -32078,13 +33337,13 @@
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>0</v>
+        <v>0.0280385686364153</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>-0.03951307545388416</v>
+        <v>-0.01258239689561835</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>-0.1715055840360835</v>
+        <v>-0.1482757864891924</v>
       </c>
       <c r="K37" s="29" t="inlineStr">
         <is>
@@ -32092,13 +33351,13 @@
         </is>
       </c>
       <c r="L37" s="31" t="n">
-        <v>0</v>
+        <v>0.01417568745709641</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>-0.09706660707616444</v>
+        <v>-0.08426690550350047</v>
       </c>
       <c r="N37" s="31" t="n">
-        <v>-0.3439301744164684</v>
+        <v>-0.3346299336189644</v>
       </c>
       <c r="P37" s="20" t="inlineStr">
         <is>
@@ -32122,13 +33381,13 @@
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>0</v>
+        <v>0.0238133043279114</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>-0.09056684903957479</v>
+        <v>-0.06891024064986284</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>-0.1741971004697684</v>
+        <v>-0.1545320047083835</v>
       </c>
       <c r="K38" s="26" t="inlineStr">
         <is>
@@ -32136,13 +33395,13 @@
         </is>
       </c>
       <c r="L38" s="28" t="n">
-        <v>-0.001607212857702867</v>
+        <v>0.009547128132854299</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>-0.0474461650686799</v>
+        <v>-0.03683849541056287</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>-0.2326590588215318</v>
+        <v>-0.2245380639089124</v>
       </c>
       <c r="P38" s="29" t="inlineStr">
         <is>
@@ -32150,13 +33409,13 @@
         </is>
       </c>
       <c r="Q38" s="31" t="n">
-        <v>0</v>
+        <v>0.04036341045520087</v>
       </c>
       <c r="R38" s="31" t="n">
-        <v>-0.05509072869796416</v>
+        <v>-0.0169509679374753</v>
       </c>
       <c r="S38" s="31" t="n">
-        <v>-0.2979170139193024</v>
+        <v>-0.2695785501785141</v>
       </c>
     </row>
     <row r="39">
@@ -32167,17 +33426,17 @@
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>MediaTek (TW)</t>
+          <t>Credo (US)</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>0</v>
+        <v>0.02620680824428412</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>-0.04637336504161715</v>
+        <v>-0.1253399917141093</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>-0.2258687258687259</v>
+        <v>-0.2150498763353421</v>
       </c>
       <c r="P39" s="26" t="inlineStr">
         <is>
@@ -32185,13 +33444,13 @@
         </is>
       </c>
       <c r="Q39" s="28" t="n">
-        <v>-0.0032878905136509</v>
+        <v>0.01111154755888828</v>
       </c>
       <c r="R39" s="28" t="n">
-        <v>-0.01505387343570479</v>
+        <v>-0.0008083393780932753</v>
       </c>
       <c r="S39" s="28" t="n">
-        <v>-0.07514107741983686</v>
+        <v>-0.06180501439481684</v>
       </c>
     </row>
     <row r="40">
@@ -32217,17 +33476,17 @@
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>Credo (US)</t>
+          <t>MediaTek (TW)</t>
         </is>
       </c>
       <c r="G40" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>-0.1476766658931756</v>
+        <v>-0.04637336504161715</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>-0.2350955798007102</v>
+        <v>-0.2258687258687259</v>
       </c>
       <c r="K40" s="19" t="inlineStr">
         <is>
@@ -32256,13 +33515,13 @@
         </is>
       </c>
       <c r="G41" s="22" t="n">
-        <v>0</v>
+        <v>0.009138303274421222</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>-0.1026588885778231</v>
+        <v>-0.09445871336104106</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>-0.2924668197107656</v>
+        <v>-0.2860011669325668</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -32311,13 +33570,13 @@
         </is>
       </c>
       <c r="G42" s="31" t="n">
-        <v>0</v>
+        <v>0.06190274406463003</v>
       </c>
       <c r="H42" s="31" t="n">
-        <v>-0.07770226258967172</v>
+        <v>-0.02060950179937282</v>
       </c>
       <c r="I42" s="31" t="n">
-        <v>-0.3687575206318787</v>
+        <v>-0.3296818789888314</v>
       </c>
       <c r="K42" s="29" t="inlineStr">
         <is>
@@ -32375,13 +33634,13 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>0.002525396373302957</v>
+        <v>0.01854630780299037</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>-0.04834840037972253</v>
+        <v>-0.03332767197985786</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>-0.138591160339667</v>
+        <v>-0.1259413261090871</v>
       </c>
       <c r="K43" s="20" t="inlineStr">
         <is>
@@ -32542,17 +33801,17 @@
       </c>
       <c r="K46" s="20" t="inlineStr">
         <is>
-          <t>Resonac (JP)</t>
+          <t>Entegris (US)</t>
         </is>
       </c>
       <c r="L46" s="22" t="n">
-        <v>-0.03432137285491421</v>
+        <v>0.04237285732386131</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>-0.2041144326583092</v>
+        <v>-0.02975368754937968</v>
       </c>
       <c r="N46" s="22" t="n">
-        <v>-0.1090320259086002</v>
+        <v>-0.07206670204263388</v>
       </c>
       <c r="P46" s="20" t="inlineStr">
         <is>
@@ -32572,17 +33831,17 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>Towa (JP)</t>
+          <t>ASML (NL)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n">
-        <v>-0.0152439024390244</v>
+        <v>0.01215165733082757</v>
       </c>
       <c r="C47" s="22" t="n">
-        <v>-0.1077348066298343</v>
+        <v>-0.03413228597174855</v>
       </c>
       <c r="D47" s="22" t="n">
-        <v>-0.09734513274336287</v>
+        <v>-0.08982207094632322</v>
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
@@ -32600,17 +33859,17 @@
       </c>
       <c r="K47" s="20" t="inlineStr">
         <is>
-          <t>Entegris (US)</t>
+          <t>Resonac (JP)</t>
         </is>
       </c>
       <c r="L47" s="22" t="n">
-        <v>0</v>
+        <v>-0.03432137285491421</v>
       </c>
       <c r="M47" s="22" t="n">
-        <v>-0.06919457309970167</v>
+        <v>-0.2041144326583092</v>
       </c>
       <c r="N47" s="22" t="n">
-        <v>-0.1097875472892702</v>
+        <v>-0.1090320259086002</v>
       </c>
       <c r="P47" s="20" t="inlineStr">
         <is>
@@ -32630,17 +33889,17 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>ASML (NL)</t>
+          <t>Towa (JP)</t>
         </is>
       </c>
       <c r="B48" s="22" t="n">
-        <v>0</v>
+        <v>-0.0152439024390244</v>
       </c>
       <c r="C48" s="22" t="n">
-        <v>-0.04572826904678773</v>
+        <v>-0.1077348066298343</v>
       </c>
       <c r="D48" s="22" t="n">
-        <v>-0.1007494554186361</v>
+        <v>-0.09734513274336287</v>
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
@@ -32720,13 +33979,13 @@
         </is>
       </c>
       <c r="L49" s="28" t="n">
-        <v>-0.01439813989494914</v>
+        <v>-0.008344874562968951</v>
       </c>
       <c r="M49" s="28" t="n">
-        <v>-0.08528397119540243</v>
+        <v>-0.07964955897392786</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>-0.06544095598724184</v>
+        <v>-0.06005226380915093</v>
       </c>
       <c r="P49" s="20" t="inlineStr">
         <is>
@@ -32794,13 +34053,13 @@
         </is>
       </c>
       <c r="B51" s="22" t="n">
-        <v>0</v>
+        <v>0.01599479804440507</v>
       </c>
       <c r="C51" s="22" t="n">
-        <v>-0.02428705688424815</v>
+        <v>-0.008680725409799583</v>
       </c>
       <c r="D51" s="22" t="n">
-        <v>-0.1583997950261505</v>
+        <v>-0.1449385697134639</v>
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
@@ -32839,17 +34098,17 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>Camtek (IL)</t>
+          <t>Applied Materials (US)</t>
         </is>
       </c>
       <c r="B52" s="22" t="n">
-        <v>0</v>
+        <v>0.02743613182972804</v>
       </c>
       <c r="C52" s="22" t="n">
-        <v>-0.06033813116167974</v>
+        <v>-0.06177528967728529</v>
       </c>
       <c r="D52" s="22" t="n">
-        <v>-0.1995242919295865</v>
+        <v>-0.1796342476657243</v>
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
@@ -32891,29 +34150,29 @@
         </is>
       </c>
       <c r="Q52" s="22" t="n">
-        <v>0</v>
+        <v>0.01592658069241004</v>
       </c>
       <c r="R52" s="22" t="n">
-        <v>-0.07710516362143449</v>
+        <v>-0.06240660453924274</v>
       </c>
       <c r="S52" s="22" t="n">
-        <v>-0.1056253064559564</v>
+        <v>-0.09138097572997761</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>Applied Materials (US)</t>
+          <t>Camtek (IL)</t>
         </is>
       </c>
       <c r="B53" s="22" t="n">
-        <v>0</v>
+        <v>0.01774507949405701</v>
       </c>
       <c r="C53" s="22" t="n">
-        <v>-0.08682916508702065</v>
+        <v>-0.04366375660160948</v>
       </c>
       <c r="D53" s="22" t="n">
-        <v>-0.2015408774136523</v>
+        <v>-0.1853197868568155</v>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
@@ -32935,13 +34194,13 @@
         </is>
       </c>
       <c r="L53" s="31" t="n">
-        <v>0</v>
+        <v>0.03511735083351675</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>0</v>
+        <v>0.03511735083351675</v>
       </c>
       <c r="N53" s="31" t="n">
-        <v>0.0005636749080946135</v>
+        <v>0.03570082051111489</v>
       </c>
       <c r="P53" s="20" t="inlineStr">
         <is>
@@ -32961,31 +34220,31 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>Teradyne (US)</t>
+          <t>KLA (US)</t>
         </is>
       </c>
       <c r="B54" s="22" t="n">
-        <v>0</v>
+        <v>0.02472361849066362</v>
       </c>
       <c r="C54" s="22" t="n">
-        <v>-0.07951596808883454</v>
+        <v>-0.1033052152232102</v>
       </c>
       <c r="D54" s="22" t="n">
-        <v>-0.2253379713254636</v>
+        <v>-0.20767841487505</v>
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>Gigabyte (TW)</t>
+          <t>HPE (US)</t>
         </is>
       </c>
       <c r="G54" s="22" t="n">
-        <v>0</v>
+        <v>0.03580883124307799</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>-0.008522727272727293</v>
+        <v>0.05101131811892468</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>-0.04774897680763979</v>
+        <v>-0.03785019834175984</v>
       </c>
       <c r="K54" s="20" t="inlineStr">
         <is>
@@ -33019,31 +34278,31 @@
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>KLA (US)</t>
+          <t>Teradyne (US)</t>
         </is>
       </c>
       <c r="B55" s="22" t="n">
-        <v>0</v>
+        <v>0.0004856528849608299</v>
       </c>
       <c r="C55" s="22" t="n">
-        <v>-0.1249398680811613</v>
+        <v>-0.07906893236317636</v>
       </c>
       <c r="D55" s="22" t="n">
-        <v>-0.2267948441629787</v>
+        <v>-0.2249617544763681</v>
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>Quanta (TW)</t>
+          <t>Gigabyte (TW)</t>
         </is>
       </c>
       <c r="G55" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>0.0238473767885532</v>
+        <v>-0.008522727272727293</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>-0.05847953216374269</v>
+        <v>-0.04774897680763979</v>
       </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
@@ -33051,13 +34310,13 @@
         </is>
       </c>
       <c r="L55" s="22" t="n">
-        <v>0</v>
+        <v>0.04892894033702166</v>
       </c>
       <c r="M55" s="22" t="n">
-        <v>-0.069552590332294</v>
+        <v>-0.0240267845379265</v>
       </c>
       <c r="N55" s="22" t="n">
-        <v>-0.1310505429588571</v>
+        <v>-0.08853376681940361</v>
       </c>
       <c r="P55" s="20" t="inlineStr">
         <is>
@@ -33081,41 +34340,41 @@
         </is>
       </c>
       <c r="B56" s="22" t="n">
-        <v>0</v>
+        <v>0.03215990308646632</v>
       </c>
       <c r="C56" s="22" t="n">
-        <v>-0.1546657024816552</v>
+        <v>-0.1274798333977992</v>
       </c>
       <c r="D56" s="22" t="n">
-        <v>-0.260033404854411</v>
+        <v>-0.2362361508673063</v>
       </c>
       <c r="F56" s="20" t="inlineStr">
         <is>
-          <t>HPE (US)</t>
+          <t>Quanta (TW)</t>
         </is>
       </c>
       <c r="G56" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>0.014676923402557</v>
+        <v>0.0238473767885532</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>-0.07111257151229278</v>
+        <v>-0.05847953216374269</v>
       </c>
       <c r="K56" s="20" t="inlineStr">
         <is>
-          <t>Sumitomo Electric (JP)</t>
+          <t>Lumentum (US)</t>
         </is>
       </c>
       <c r="L56" s="22" t="n">
-        <v>-0.03519781718963166</v>
+        <v>0.08189956501240725</v>
       </c>
       <c r="M56" s="22" t="n">
-        <v>-0.146512189234854</v>
+        <v>-0.01966427482912558</v>
       </c>
       <c r="N56" s="22" t="n">
-        <v>-0.1502042778178323</v>
+        <v>-0.1348990764533324</v>
       </c>
       <c r="P56" s="20" t="inlineStr">
         <is>
@@ -33153,13 +34412,13 @@
         </is>
       </c>
       <c r="G57" s="22" t="n">
-        <v>0</v>
+        <v>0.006241528077742364</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>-0.02868182800792252</v>
+        <v>-0.02261931836501252</v>
       </c>
       <c r="I57" s="22" t="n">
-        <v>-0.1133083323217764</v>
+        <v>-0.1077740213816626</v>
       </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
@@ -33167,13 +34426,13 @@
         </is>
       </c>
       <c r="L57" s="22" t="n">
-        <v>0</v>
+        <v>0.02825323730307949</v>
       </c>
       <c r="M57" s="22" t="n">
-        <v>-0.05783001917211206</v>
+        <v>-0.03121066712394382</v>
       </c>
       <c r="N57" s="22" t="n">
-        <v>-0.1599493490604679</v>
+        <v>-0.1362151986728669</v>
       </c>
       <c r="P57" s="29" t="inlineStr">
         <is>
@@ -33181,13 +34440,13 @@
         </is>
       </c>
       <c r="Q57" s="31" t="n">
-        <v>0</v>
+        <v>0.06728247844941304</v>
       </c>
       <c r="R57" s="31" t="n">
-        <v>-0.1916246029885517</v>
+        <v>-0.1372351027600932</v>
       </c>
       <c r="S57" s="31" t="n">
-        <v>-0.3715384024226365</v>
+        <v>-0.3292539485273539</v>
       </c>
     </row>
     <row r="58">
@@ -33197,13 +34456,13 @@
         </is>
       </c>
       <c r="B58" s="31" t="n">
-        <v>0</v>
+        <v>0.02441114496833197</v>
       </c>
       <c r="C58" s="31" t="n">
-        <v>-0.1219728047216202</v>
+        <v>-0.1005391555715417</v>
       </c>
       <c r="D58" s="31" t="n">
-        <v>-0.2999542144925217</v>
+        <v>-0.2828652953380288</v>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
@@ -33221,17 +34480,17 @@
       </c>
       <c r="K58" s="20" t="inlineStr">
         <is>
-          <t>Fujikura (JP)</t>
+          <t>Sumitomo Electric (JP)</t>
         </is>
       </c>
       <c r="L58" s="22" t="n">
-        <v>-0.01461481297993561</v>
+        <v>-0.03519781718963166</v>
       </c>
       <c r="M58" s="22" t="n">
-        <v>-0.1124497991967871</v>
+        <v>-0.146512189234854</v>
       </c>
       <c r="N58" s="22" t="n">
-        <v>-0.1966882067851373</v>
+        <v>-0.1502042778178323</v>
       </c>
       <c r="P58" s="26" t="inlineStr">
         <is>
@@ -33239,13 +34498,13 @@
         </is>
       </c>
       <c r="Q58" s="28" t="n">
-        <v>-0.002186623708569294</v>
+        <v>0.003360646900885578</v>
       </c>
       <c r="R58" s="28" t="n">
-        <v>-0.06733000718190611</v>
+        <v>-0.06272413656119609</v>
       </c>
       <c r="S58" s="28" t="n">
-        <v>-0.06163214542487823</v>
+        <v>-0.05786355978346081</v>
       </c>
     </row>
     <row r="59">
@@ -33255,13 +34514,13 @@
         </is>
       </c>
       <c r="B59" s="28" t="n">
-        <v>-0.01582935637744281</v>
+        <v>-0.007212246036918341</v>
       </c>
       <c r="C59" s="28" t="n">
-        <v>-0.09917519986668422</v>
+        <v>-0.09141787923685994</v>
       </c>
       <c r="D59" s="28" t="n">
-        <v>-0.1301708510203809</v>
+        <v>-0.1234553752490298</v>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
@@ -33269,27 +34528,27 @@
         </is>
       </c>
       <c r="G59" s="22" t="n">
-        <v>0</v>
+        <v>0.02333273560494198</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>0.002195678892147113</v>
+        <v>0.02557964569215287</v>
       </c>
       <c r="I59" s="22" t="n">
-        <v>-0.1684762503606769</v>
+        <v>-0.1490745265611128</v>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
-          <t>Lumentum (US)</t>
+          <t>Fabrinet (US)</t>
         </is>
       </c>
       <c r="L59" s="22" t="n">
-        <v>0</v>
+        <v>0.03270460314067281</v>
       </c>
       <c r="M59" s="22" t="n">
-        <v>-0.09387547895018156</v>
+        <v>-0.1032562572856731</v>
       </c>
       <c r="N59" s="22" t="n">
-        <v>-0.2003870308084036</v>
+        <v>-0.1945517581314837</v>
       </c>
     </row>
     <row r="60">
@@ -33299,27 +34558,27 @@
         </is>
       </c>
       <c r="G60" s="22" t="n">
-        <v>0</v>
+        <v>-0.007589557086298493</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>0.0261682302964934</v>
+        <v>0.01838006793251235</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>-0.2070294198189038</v>
+        <v>-0.2130477153049435</v>
       </c>
       <c r="K60" s="20" t="inlineStr">
         <is>
-          <t>Fabrinet (US)</t>
+          <t>Fujikura (JP)</t>
         </is>
       </c>
       <c r="L60" s="22" t="n">
-        <v>0</v>
+        <v>-0.01461481297993561</v>
       </c>
       <c r="M60" s="22" t="n">
-        <v>-0.1316551315960637</v>
+        <v>-0.1124497991967871</v>
       </c>
       <c r="N60" s="22" t="n">
-        <v>-0.2200594057400558</v>
+        <v>-0.1966882067851373</v>
       </c>
       <c r="P60" s="19" t="inlineStr">
         <is>
@@ -33339,13 +34598,13 @@
         </is>
       </c>
       <c r="G61" s="31" t="n">
-        <v>0</v>
+        <v>-0.0513826982322082</v>
       </c>
       <c r="H61" s="31" t="n">
-        <v>-0.1343099567775186</v>
+        <v>-0.1787914470310467</v>
       </c>
       <c r="I61" s="31" t="n">
-        <v>-0.2698193927388406</v>
+        <v>-0.3073380425367513</v>
       </c>
       <c r="K61" s="20" t="inlineStr">
         <is>
@@ -33409,13 +34668,13 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>6.934908376508749e-05</v>
+        <v>0.0004967383909154632</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>-0.001851301531372969</v>
+        <v>-0.0009505536285880171</v>
       </c>
       <c r="I62" s="28" t="n">
-        <v>-0.06154662173300917</v>
+        <v>-0.06056919089125847</v>
       </c>
       <c r="K62" s="29" t="inlineStr">
         <is>
@@ -33423,13 +34682,13 @@
         </is>
       </c>
       <c r="L62" s="31" t="n">
-        <v>0</v>
+        <v>0.05834013620122858</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>-0.09796573815952647</v>
+        <v>-0.04534093646557869</v>
       </c>
       <c r="N62" s="31" t="n">
-        <v>-0.325719309871535</v>
+        <v>-0.2863816825715819</v>
       </c>
       <c r="P62" s="29" t="inlineStr">
         <is>
@@ -33467,13 +34726,13 @@
         </is>
       </c>
       <c r="L63" s="28" t="n">
-        <v>-0.006864144343610723</v>
+        <v>0.02166023893918193</v>
       </c>
       <c r="M63" s="28" t="n">
-        <v>-0.09696474808781726</v>
+        <v>-0.07071500920767257</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>-0.1728583040936602</v>
+        <v>-0.1496861739542931</v>
       </c>
       <c r="P63" s="20" t="inlineStr">
         <is>
@@ -33596,13 +34855,13 @@
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>0</v>
+        <v>0.05623743688110272</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>-0.05376385376777437</v>
+        <v>-0.0005499582194216091</v>
       </c>
       <c r="I66" s="22" t="n">
-        <v>0.0510703374860626</v>
+        <v>0.1101798392480344</v>
       </c>
       <c r="P66" s="20" t="inlineStr">
         <is>
@@ -33626,13 +34885,13 @@
         </is>
       </c>
       <c r="B67" s="22" t="n">
-        <v>0</v>
+        <v>0.0004856528849608299</v>
       </c>
       <c r="C67" s="22" t="n">
-        <v>-0.07951596808883454</v>
+        <v>-0.07906893236317636</v>
       </c>
       <c r="D67" s="22" t="n">
-        <v>-0.2253379713254636</v>
+        <v>-0.2249617544763681</v>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
@@ -33640,13 +34899,13 @@
         </is>
       </c>
       <c r="G67" s="22" t="n">
-        <v>0</v>
+        <v>0.0179469283978082</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>-0.02875466623211942</v>
+        <v>-0.01132379577028186</v>
       </c>
       <c r="I67" s="22" t="n">
-        <v>0.04469376953875392</v>
+        <v>0.0634428138183023</v>
       </c>
       <c r="P67" s="20" t="inlineStr">
         <is>
@@ -33654,13 +34913,13 @@
         </is>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>0</v>
+        <v>0.01586962472654951</v>
       </c>
       <c r="R67" s="22" t="n">
-        <v>-0.06485316640724781</v>
+        <v>-0.05001273709390963</v>
       </c>
       <c r="S67" s="22" t="n">
-        <v>-0.172614085218868</v>
+        <v>-0.1594837812472585</v>
       </c>
     </row>
     <row r="68">
@@ -33670,13 +34929,13 @@
         </is>
       </c>
       <c r="B68" s="31" t="n">
-        <v>0</v>
+        <v>-0.0633587254989415</v>
       </c>
       <c r="C68" s="31" t="n">
-        <v>-0.06182860325435846</v>
+        <v>-0.1212699472517241</v>
       </c>
       <c r="D68" s="31" t="n">
-        <v>-0.2800879441800571</v>
+        <v>-0.3257006545081315</v>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
@@ -33684,13 +34943,13 @@
         </is>
       </c>
       <c r="G68" s="22" t="n">
-        <v>0</v>
+        <v>0.06190274406463003</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>-0.07770226258967172</v>
+        <v>-0.02060950179937282</v>
       </c>
       <c r="I68" s="22" t="n">
-        <v>-0.3687575206318787</v>
+        <v>-0.3296818789888314</v>
       </c>
       <c r="P68" s="20" t="inlineStr">
         <is>
@@ -33698,13 +34957,13 @@
         </is>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>0</v>
+        <v>0.02809793767642388</v>
       </c>
       <c r="R68" s="22" t="n">
-        <v>-0.05706519022877743</v>
+        <v>-0.03057066671089503</v>
       </c>
       <c r="S68" s="22" t="n">
-        <v>-0.2333306944807747</v>
+        <v>-0.2117888681158683</v>
       </c>
     </row>
     <row r="69">
@@ -33714,13 +34973,13 @@
         </is>
       </c>
       <c r="B69" s="28" t="n">
-        <v>-0.006545042259327967</v>
+        <v>-0.01702388769499141</v>
       </c>
       <c r="C69" s="28" t="n">
-        <v>-0.05402794380854498</v>
+        <v>-0.06386032852049622</v>
       </c>
       <c r="D69" s="28" t="n">
-        <v>-0.152481569433195</v>
+        <v>-0.1600209850130248</v>
       </c>
       <c r="F69" s="26" t="inlineStr">
         <is>
@@ -33728,13 +34987,13 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>0</v>
+        <v>0.04536236978118032</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>-0.05340692752985517</v>
+        <v>-0.0108277519296921</v>
       </c>
       <c r="I69" s="28" t="n">
-        <v>-0.0909978045356874</v>
+        <v>-0.05201974197416489</v>
       </c>
       <c r="P69" s="29" t="inlineStr">
         <is>
@@ -33758,13 +35017,13 @@
         </is>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>-0.001719262005324088</v>
+        <v>0.003776683295047586</v>
       </c>
       <c r="R70" s="28" t="n">
-        <v>-0.04295789052944621</v>
+        <v>-0.03779102142554364</v>
       </c>
       <c r="S70" s="28" t="n">
-        <v>-0.1608054443530018</v>
+        <v>-0.1564714280609373</v>
       </c>
     </row>
   </sheetData>
